--- a/data/live/BallparkPal_Teams_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Teams_2026-04-12.xlsx
@@ -665,7 +665,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>822828</v>
+        <v>822998</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -679,150 +679,150 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t xml:space="preserve">TB </t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.738</v>
+        <v>4.505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.532</v>
+        <v>0.582</v>
       </c>
       <c r="H2" t="n">
-        <v>0.101</v>
+        <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>0.319</v>
       </c>
       <c r="J2" t="n">
-        <v>0.099</v>
+        <v>0.082</v>
       </c>
       <c r="K2" t="n">
-        <v>0.188</v>
+        <v>0.163</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.385</v>
       </c>
       <c r="M2" t="n">
-        <v>0.103</v>
+        <v>0.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.645</v>
+        <v>1.501</v>
       </c>
       <c r="O2" t="n">
-        <v>4.978</v>
+        <v>4.503</v>
       </c>
       <c r="P2" t="n">
-        <v>3.481</v>
+        <v>3.662</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.834</v>
+        <v>9.246</v>
       </c>
       <c r="R2" t="n">
-        <v>0.226</v>
+        <v>0.272</v>
       </c>
       <c r="S2" t="n">
-        <v>0.333</v>
+        <v>0.33</v>
       </c>
       <c r="T2" t="n">
-        <v>0.251</v>
+        <v>0.222</v>
       </c>
       <c r="U2" t="n">
-        <v>0.123</v>
+        <v>0.117</v>
       </c>
       <c r="V2" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="W2" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="X2" t="n">
-        <v>0.039</v>
+        <v>0.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.142</v>
+        <v>0.145</v>
       </c>
       <c r="AC2" t="n">
         <v>0.119</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.107</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.055</v>
+        <v>0.058</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.047</v>
+        <v>0.035</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.01</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AM2" t="n">
         <v>0.004</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.629</v>
+        <v>0.504</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.55</v>
+        <v>0.385</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.585</v>
+        <v>0.456</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.556</v>
+        <v>0.457</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.52</v>
+        <v>0.431</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.464</v>
+        <v>0.501</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.414</v>
+        <v>0.489</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.421</v>
+        <v>0.513</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.383</v>
+        <v>0.514</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.115</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>823154</v>
+        <v>823075</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -836,150 +836,150 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.934</v>
+        <v>4.705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.43</v>
+        <v>0.533</v>
       </c>
       <c r="H3" t="n">
-        <v>0.094</v>
+        <v>0.113</v>
       </c>
       <c r="I3" t="n">
-        <v>0.212</v>
+        <v>0.294</v>
       </c>
       <c r="J3" t="n">
-        <v>0.108</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.275</v>
+        <v>0.233</v>
       </c>
       <c r="L3" t="n">
-        <v>1.195</v>
+        <v>0.857</v>
       </c>
       <c r="M3" t="n">
-        <v>0.075</v>
+        <v>0.161</v>
       </c>
       <c r="N3" t="n">
-        <v>1.373</v>
+        <v>1.787</v>
       </c>
       <c r="O3" t="n">
-        <v>5.081</v>
+        <v>5.603</v>
       </c>
       <c r="P3" t="n">
-        <v>2.667</v>
+        <v>4.126</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.877000000000001</v>
+        <v>7.029</v>
       </c>
       <c r="R3" t="n">
-        <v>0.311</v>
+        <v>0.427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="T3" t="n">
-        <v>0.204</v>
+        <v>0.161</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09</v>
+        <v>0.044</v>
       </c>
       <c r="V3" t="n">
-        <v>0.028</v>
+        <v>0.008</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="X3" t="n">
-        <v>0.075</v>
+        <v>0.049</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.128</v>
+        <v>0.093</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.148</v>
+        <v>0.115</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.143</v>
+        <v>0.132</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.103</v>
+        <v>0.114</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.083</v>
+        <v>0.104</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.058</v>
+        <v>0.081</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="AH3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.016</v>
       </c>
-      <c r="AI3" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="AL3" t="n">
         <v>0.002</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.413</v>
+        <v>0.543</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.368</v>
+        <v>0.491</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.408</v>
+        <v>0.535</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.428</v>
+        <v>0.543</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.404</v>
+        <v>0.478</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.399</v>
+        <v>0.491</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.419</v>
+        <v>0.457</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.446</v>
+        <v>0.438</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.403</v>
+        <v>0.441</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.161</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>823479</v>
+        <v>823317</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -993,150 +993,150 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t xml:space="preserve">SD </t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.42</v>
+        <v>2.892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.433</v>
+        <v>0.289</v>
       </c>
       <c r="H4" t="n">
-        <v>0.089</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.228</v>
+        <v>0.113</v>
       </c>
       <c r="J4" t="n">
-        <v>0.111</v>
+        <v>0.137</v>
       </c>
       <c r="K4" t="n">
-        <v>0.271</v>
+        <v>0.378</v>
       </c>
       <c r="L4" t="n">
-        <v>0.839</v>
+        <v>0.951</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17</v>
+        <v>0.095</v>
       </c>
       <c r="N4" t="n">
-        <v>1.397</v>
+        <v>0.946</v>
       </c>
       <c r="O4" t="n">
-        <v>6.193</v>
+        <v>3.938</v>
       </c>
       <c r="P4" t="n">
-        <v>3.752</v>
+        <v>2.857</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.527</v>
+        <v>11.654</v>
       </c>
       <c r="R4" t="n">
-        <v>0.445</v>
+        <v>0.396</v>
       </c>
       <c r="S4" t="n">
-        <v>0.346</v>
+        <v>0.355</v>
       </c>
       <c r="T4" t="n">
-        <v>0.15</v>
+        <v>0.177</v>
       </c>
       <c r="U4" t="n">
-        <v>0.044</v>
+        <v>0.054</v>
       </c>
       <c r="V4" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="X4" t="n">
-        <v>0.061</v>
+        <v>0.147</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.109</v>
+        <v>0.179</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.14</v>
+        <v>0.187</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.134</v>
+        <v>0.154</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.126</v>
+        <v>0.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.11</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.094</v>
+        <v>0.053</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.065</v>
+        <v>0.041</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.056</v>
+        <v>0.022</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.039</v>
+        <v>0.014</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.026</v>
+        <v>0.006</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.511</v>
+        <v>0.318</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.414</v>
+        <v>0.256</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.483</v>
+        <v>0.287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.438</v>
+        <v>0.258</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.448</v>
+        <v>0.302</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.478</v>
+        <v>0.312</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.473</v>
+        <v>0.332</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.473</v>
+        <v>0.334</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.438</v>
+        <v>0.34</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.141</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>823804</v>
+        <v>823642</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1150,150 +1150,150 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.704</v>
+        <v>3.23</v>
       </c>
       <c r="G5" t="n">
-        <v>0.358</v>
+        <v>0.426</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="I5" t="n">
-        <v>0.175</v>
+        <v>0.184</v>
       </c>
       <c r="J5" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="K5" t="n">
-        <v>0.332</v>
+        <v>0.245</v>
       </c>
       <c r="L5" t="n">
-        <v>1.019</v>
+        <v>0.716</v>
       </c>
       <c r="M5" t="n">
-        <v>0.095</v>
+        <v>0.097</v>
       </c>
       <c r="N5" t="n">
-        <v>1.322</v>
+        <v>1.316</v>
       </c>
       <c r="O5" t="n">
-        <v>4.863</v>
+        <v>4.378</v>
       </c>
       <c r="P5" t="n">
-        <v>2.821</v>
+        <v>4.002</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.069000000000001</v>
+        <v>11.929</v>
       </c>
       <c r="R5" t="n">
-        <v>0.371</v>
+        <v>0.504</v>
       </c>
       <c r="S5" t="n">
-        <v>0.358</v>
+        <v>0.325</v>
       </c>
       <c r="T5" t="n">
-        <v>0.179</v>
+        <v>0.131</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="V5" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="W5" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="X5" t="n">
-        <v>0.082</v>
+        <v>0.113</v>
       </c>
       <c r="Y5" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0.147</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.153</v>
-      </c>
       <c r="AB5" t="n">
-        <v>0.134</v>
+        <v>0.129</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.105</v>
+        <v>0.096</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.067</v>
+        <v>0.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.052</v>
+        <v>0.041</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.017</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.427</v>
+        <v>0.366</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.357</v>
+        <v>0.294</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.409</v>
+        <v>0.327</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.328</v>
+        <v>0.292</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.348</v>
+        <v>0.325</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.4</v>
+        <v>0.365</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.385</v>
+        <v>0.349</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.427</v>
+        <v>0.341</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.42</v>
+        <v>0.34</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.121</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>823966</v>
+        <v>824126</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1307,76 +1307,76 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHW</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t xml:space="preserve">KC </t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.516</v>
+        <v>4.254</v>
       </c>
       <c r="G6" t="n">
-        <v>0.572</v>
+        <v>0.373</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.326</v>
+        <v>0.174</v>
       </c>
       <c r="J6" t="n">
-        <v>0.081</v>
+        <v>0.107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.164</v>
+        <v>0.338</v>
       </c>
       <c r="L6" t="n">
-        <v>1.106</v>
+        <v>1.134</v>
       </c>
       <c r="M6" t="n">
-        <v>0.108</v>
+        <v>0.045</v>
       </c>
       <c r="N6" t="n">
-        <v>1.567</v>
+        <v>1.533</v>
       </c>
       <c r="O6" t="n">
-        <v>4.648</v>
+        <v>4.987</v>
       </c>
       <c r="P6" t="n">
-        <v>4.891</v>
+        <v>3.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.007999999999999</v>
+        <v>7.715</v>
       </c>
       <c r="R6" t="n">
-        <v>0.333</v>
+        <v>0.322</v>
       </c>
       <c r="S6" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="T6" t="n">
-        <v>0.204</v>
+        <v>0.21</v>
       </c>
       <c r="U6" t="n">
-        <v>0.073</v>
+        <v>0.08</v>
       </c>
       <c r="V6" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="X6" t="n">
-        <v>0.051</v>
+        <v>0.062</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.106</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.116</v>
+        <v>0.133</v>
       </c>
       <c r="AA6" t="n">
         <v>0.149</v>
@@ -1385,72 +1385,72 @@
         <v>0.137</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.12</v>
+        <v>0.118</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.103</v>
+        <v>0.099</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.068</v>
+        <v>0.066</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.043</v>
+        <v>0.033</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AM6" t="n">
         <v>0.004</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.601</v>
+        <v>0.513</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.483</v>
+        <v>0.442</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.516</v>
+        <v>0.437</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.478</v>
+        <v>0.457</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.427</v>
+        <v>0.433</v>
       </c>
       <c r="AT6" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0.391</v>
       </c>
-      <c r="AU6" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.394</v>
-      </c>
       <c r="AW6" t="n">
-        <v>0.145</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>824533</v>
+        <v>824293</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1464,150 +1464,150 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.971</v>
+        <v>3.227</v>
       </c>
       <c r="G7" t="n">
-        <v>0.457</v>
+        <v>0.433</v>
       </c>
       <c r="H7" t="n">
-        <v>0.094</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.23</v>
+        <v>0.194</v>
       </c>
       <c r="J7" t="n">
-        <v>0.106</v>
+        <v>0.125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.256</v>
+        <v>0.239</v>
       </c>
       <c r="L7" t="n">
-        <v>1.129</v>
+        <v>0.578</v>
       </c>
       <c r="M7" t="n">
-        <v>0.082</v>
+        <v>0.151</v>
       </c>
       <c r="N7" t="n">
-        <v>1.276</v>
+        <v>1.426</v>
       </c>
       <c r="O7" t="n">
-        <v>4.589</v>
+        <v>5.16</v>
       </c>
       <c r="P7" t="n">
-        <v>3.971</v>
+        <v>2.375</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.313</v>
+        <v>10.165</v>
       </c>
       <c r="R7" t="n">
-        <v>0.321</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.368</v>
+        <v>0.325</v>
       </c>
       <c r="T7" t="n">
-        <v>0.203</v>
+        <v>0.095</v>
       </c>
       <c r="U7" t="n">
-        <v>0.083</v>
+        <v>0.015</v>
       </c>
       <c r="V7" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.081</v>
+        <v>0.126</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.13</v>
+        <v>0.166</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.136</v>
+        <v>0.171</v>
       </c>
       <c r="AA7" t="n">
         <v>0.144</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.134</v>
+        <v>0.124</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.111</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.082</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.065</v>
+        <v>0.046</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.044</v>
+        <v>0.024</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.005</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.481</v>
+        <v>0.321</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.373</v>
+        <v>0.266</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.42</v>
+        <v>0.294</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.384</v>
+        <v>0.305</v>
       </c>
       <c r="AR7" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AU7" t="n">
         <v>0.397</v>
       </c>
-      <c r="AS7" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.465</v>
-      </c>
       <c r="AV7" t="n">
-        <v>0.425</v>
+        <v>0.404</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.127</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>824859</v>
+        <v>824696</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1621,150 +1621,150 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SF </t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.28</v>
+        <v>5.907</v>
       </c>
       <c r="G8" t="n">
-        <v>0.474</v>
+        <v>0.456</v>
       </c>
       <c r="H8" t="n">
-        <v>0.097</v>
+        <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>0.255</v>
+        <v>0.282</v>
       </c>
       <c r="J8" t="n">
-        <v>0.102</v>
+        <v>0.091</v>
       </c>
       <c r="K8" t="n">
-        <v>0.237</v>
+        <v>0.304</v>
       </c>
       <c r="L8" t="n">
-        <v>0.632</v>
+        <v>1.815</v>
       </c>
       <c r="M8" t="n">
-        <v>0.133</v>
+        <v>0.122</v>
       </c>
       <c r="N8" t="n">
-        <v>1.604</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>5.909</v>
+        <v>5.318</v>
       </c>
       <c r="P8" t="n">
-        <v>4.038</v>
+        <v>3.395</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.087999999999999</v>
+        <v>8.606999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0.537</v>
+        <v>0.179</v>
       </c>
       <c r="S8" t="n">
-        <v>0.328</v>
+        <v>0.286</v>
       </c>
       <c r="T8" t="n">
-        <v>0.11</v>
+        <v>0.259</v>
       </c>
       <c r="U8" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AM8" t="n">
         <v>0.021</v>
       </c>
-      <c r="V8" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.003</v>
-      </c>
       <c r="AN8" t="n">
-        <v>0.512</v>
+        <v>0.609</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.49</v>
+        <v>0.606</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.448</v>
+        <v>0.606</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.487</v>
+        <v>0.609</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.451</v>
+        <v>0.606</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.425</v>
+        <v>0.626</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.422</v>
+        <v>0.658</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.392</v>
+        <v>0.617</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.387</v>
+        <v>0.68</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.127</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>822998</v>
+        <v>824938</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1778,150 +1778,150 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB </t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.637</v>
+        <v>3.666</v>
       </c>
       <c r="G9" t="n">
-        <v>0.595</v>
+        <v>0.43</v>
       </c>
       <c r="H9" t="n">
-        <v>0.119</v>
+        <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.349</v>
+        <v>0.21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="K9" t="n">
-        <v>0.153</v>
+        <v>0.273</v>
       </c>
       <c r="L9" t="n">
-        <v>1.553</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.117</v>
+        <v>0.066</v>
       </c>
       <c r="N9" t="n">
-        <v>1.486</v>
+        <v>1.59</v>
       </c>
       <c r="O9" t="n">
-        <v>4.274</v>
+        <v>5.101</v>
       </c>
       <c r="P9" t="n">
-        <v>3.88</v>
+        <v>3.084</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.85</v>
+        <v>10.027</v>
       </c>
       <c r="R9" t="n">
-        <v>0.223</v>
+        <v>0.451</v>
       </c>
       <c r="S9" t="n">
-        <v>0.321</v>
+        <v>0.352</v>
       </c>
       <c r="T9" t="n">
-        <v>0.247</v>
+        <v>0.142</v>
       </c>
       <c r="U9" t="n">
-        <v>0.132</v>
+        <v>0.043</v>
       </c>
       <c r="V9" t="n">
-        <v>0.052</v>
+        <v>0.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0.026</v>
+        <v>0.002</v>
       </c>
       <c r="X9" t="n">
-        <v>0.053</v>
+        <v>0.093</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.092</v>
+        <v>0.141</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.124</v>
+        <v>0.148</v>
       </c>
       <c r="AA9" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AB9" t="n">
         <v>0.134</v>
       </c>
-      <c r="AB9" t="n">
-        <v>0.135</v>
-      </c>
       <c r="AC9" t="n">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.102</v>
+        <v>0.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.076</v>
+        <v>0.048</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.05</v>
+        <v>0.032</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AL9" t="n">
         <v>0.002</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.529</v>
+        <v>0.421</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.394</v>
+        <v>0.348</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.471</v>
+        <v>0.405</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.447</v>
+        <v>0.36</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.465</v>
+        <v>0.39</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.517</v>
+        <v>0.387</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.525</v>
+        <v>0.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.528</v>
+        <v>0.367</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.535</v>
+        <v>0.356</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.15</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>823075</v>
+        <v>822828</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1935,103 +1935,103 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.616</v>
+        <v>4.793</v>
       </c>
       <c r="G10" t="n">
-        <v>0.534</v>
+        <v>0.541</v>
       </c>
       <c r="H10" t="n">
-        <v>0.102</v>
+        <v>0.104</v>
       </c>
       <c r="I10" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="J10" t="n">
-        <v>0.089</v>
+        <v>0.096</v>
       </c>
       <c r="K10" t="n">
-        <v>0.228</v>
+        <v>0.188</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9</v>
+        <v>1.501</v>
       </c>
       <c r="M10" t="n">
-        <v>0.16</v>
+        <v>0.098</v>
       </c>
       <c r="N10" t="n">
-        <v>1.751</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>5.378</v>
+        <v>4.871</v>
       </c>
       <c r="P10" t="n">
-        <v>4.093</v>
+        <v>3.506</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.006</v>
+        <v>8.977</v>
       </c>
       <c r="R10" t="n">
-        <v>0.408</v>
+        <v>0.226</v>
       </c>
       <c r="S10" t="n">
-        <v>0.365</v>
+        <v>0.322</v>
       </c>
       <c r="T10" t="n">
-        <v>0.162</v>
+        <v>0.261</v>
       </c>
       <c r="U10" t="n">
-        <v>0.051</v>
+        <v>0.126</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="X10" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.091</v>
+        <v>0.077</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.136</v>
+        <v>0.128</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.118</v>
+        <v>0.13</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1</v>
+        <v>0.108</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.052</v>
+        <v>0.066</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.011</v>
@@ -2046,39 +2046,39 @@
         <v>0.004</v>
       </c>
       <c r="AN10" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="AO10" t="n">
         <v>0.547</v>
       </c>
-      <c r="AO10" t="n">
-        <v>0.504</v>
-      </c>
       <c r="AP10" t="n">
-        <v>0.495</v>
+        <v>0.593</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.505</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.506</v>
+        <v>0.511</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.488</v>
+        <v>0.491</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.429</v>
+        <v>0.432</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.424</v>
+        <v>0.418</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.464</v>
+        <v>0.404</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.141</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>823317</v>
+        <v>823154</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2092,150 +2092,150 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD </t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.791</v>
+        <v>3.941</v>
       </c>
       <c r="G11" t="n">
-        <v>0.307</v>
+        <v>0.426</v>
       </c>
       <c r="H11" t="n">
-        <v>0.077</v>
+        <v>0.089</v>
       </c>
       <c r="I11" t="n">
-        <v>0.118</v>
+        <v>0.21</v>
       </c>
       <c r="J11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.015</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.553000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.143</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.909</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.904</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>11.467</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AW11" t="n">
         <v>0.156</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>823642</v>
+        <v>823479</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2249,150 +2249,150 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.227</v>
+        <v>4.257</v>
       </c>
       <c r="G12" t="n">
-        <v>0.409</v>
+        <v>0.436</v>
       </c>
       <c r="H12" t="n">
-        <v>0.094</v>
+        <v>0.079</v>
       </c>
       <c r="I12" t="n">
-        <v>0.186</v>
+        <v>0.25</v>
       </c>
       <c r="J12" t="n">
-        <v>0.122</v>
+        <v>0.113</v>
       </c>
       <c r="K12" t="n">
-        <v>0.257</v>
+        <v>0.267</v>
       </c>
       <c r="L12" t="n">
-        <v>0.709</v>
+        <v>0.822</v>
       </c>
       <c r="M12" t="n">
-        <v>0.097</v>
+        <v>0.152</v>
       </c>
       <c r="N12" t="n">
-        <v>1.408</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>4.249</v>
+        <v>6.048</v>
       </c>
       <c r="P12" t="n">
-        <v>3.892</v>
+        <v>3.532</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.561</v>
+        <v>7.845</v>
       </c>
       <c r="R12" t="n">
-        <v>0.498</v>
+        <v>0.449</v>
       </c>
       <c r="S12" t="n">
-        <v>0.342</v>
+        <v>0.349</v>
       </c>
       <c r="T12" t="n">
-        <v>0.119</v>
+        <v>0.146</v>
       </c>
       <c r="U12" t="n">
-        <v>0.034</v>
+        <v>0.045</v>
       </c>
       <c r="V12" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="W12" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="X12" t="n">
-        <v>0.13</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.16</v>
+        <v>0.123</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.165</v>
+        <v>0.132</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.151</v>
+        <v>0.136</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.128</v>
+        <v>0.132</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.094</v>
+        <v>0.109</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.062</v>
+        <v>0.082</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.04</v>
+        <v>0.073</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.027</v>
+        <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="AH12" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.011</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.001</v>
       </c>
       <c r="AK12" t="n">
         <v>0.003</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.363</v>
+        <v>0.466</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.322</v>
+        <v>0.396</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.331</v>
+        <v>0.485</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.32</v>
+        <v>0.435</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.334</v>
+        <v>0.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.341</v>
+        <v>0.477</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.336</v>
+        <v>0.43</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.34</v>
+        <v>0.433</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.323</v>
+        <v>0.415</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.139</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>824126</v>
+        <v>823804</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2406,150 +2406,150 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC </t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.296</v>
+        <v>3.665</v>
       </c>
       <c r="G13" t="n">
-        <v>0.349</v>
+        <v>0.353</v>
       </c>
       <c r="H13" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9.076000000000001</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.219</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.481</v>
-      </c>
-      <c r="O13" t="n">
-        <v>5.039</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.095</v>
-      </c>
       <c r="AE13" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05</v>
+        <v>0.036</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.036</v>
+        <v>0.025</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="AJ13" t="n">
         <v>0.006</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.528</v>
+        <v>0.404</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.447</v>
+        <v>0.318</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.471</v>
+        <v>0.391</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.482</v>
+        <v>0.369</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.449</v>
+        <v>0.391</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.438</v>
+        <v>0.379</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.426</v>
+        <v>0.39</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.432</v>
+        <v>0.42</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.425</v>
+        <v>0.414</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>824293</v>
+        <v>823966</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2563,150 +2563,150 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.371</v>
+        <v>4.783</v>
       </c>
       <c r="G14" t="n">
-        <v>0.446</v>
+        <v>0.579</v>
       </c>
       <c r="H14" t="n">
-        <v>0.095</v>
+        <v>0.118</v>
       </c>
       <c r="I14" t="n">
-        <v>0.215</v>
+        <v>0.33</v>
       </c>
       <c r="J14" t="n">
-        <v>0.123</v>
+        <v>0.081</v>
       </c>
       <c r="K14" t="n">
-        <v>0.238</v>
+        <v>0.158</v>
       </c>
       <c r="L14" t="n">
-        <v>0.604</v>
+        <v>1.201</v>
       </c>
       <c r="M14" t="n">
-        <v>0.134</v>
+        <v>0.111</v>
       </c>
       <c r="N14" t="n">
-        <v>1.471</v>
+        <v>1.606</v>
       </c>
       <c r="O14" t="n">
-        <v>5.296</v>
+        <v>4.792</v>
       </c>
       <c r="P14" t="n">
-        <v>2.472</v>
+        <v>4.908</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.159</v>
+        <v>8.997999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>0.555</v>
+        <v>0.304</v>
       </c>
       <c r="S14" t="n">
-        <v>0.316</v>
+        <v>0.369</v>
       </c>
       <c r="T14" t="n">
-        <v>0.104</v>
+        <v>0.197</v>
       </c>
       <c r="U14" t="n">
-        <v>0.023</v>
+        <v>0.093</v>
       </c>
       <c r="V14" t="n">
-        <v>0.003</v>
+        <v>0.024</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="X14" t="n">
-        <v>0.116</v>
+        <v>0.041</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.154</v>
+        <v>0.091</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.156</v>
+        <v>0.122</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.154</v>
+        <v>0.137</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.131</v>
+        <v>0.141</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.101</v>
+        <v>0.114</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.049</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.029</v>
+        <v>0.056</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.016</v>
+        <v>0.042</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AL14" t="n">
         <v>0.005</v>
       </c>
-      <c r="AK14" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AM14" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.326</v>
+        <v>0.585</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.294</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.286</v>
+        <v>0.57</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.332</v>
+        <v>0.526</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.332</v>
+        <v>0.491</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.334</v>
+        <v>0.458</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.377</v>
+        <v>0.457</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.401</v>
+        <v>0.456</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.407</v>
+        <v>0.432</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.184</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>824696</v>
+        <v>824533</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2720,150 +2720,150 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.14</v>
+        <v>3.95</v>
       </c>
       <c r="G15" t="n">
-        <v>0.441</v>
+        <v>0.456</v>
       </c>
       <c r="H15" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.098</v>
       </c>
       <c r="I15" t="n">
-        <v>0.281</v>
+        <v>0.22</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="K15" t="n">
-        <v>0.315</v>
+        <v>0.242</v>
       </c>
       <c r="L15" t="n">
-        <v>1.94</v>
+        <v>1.004</v>
       </c>
       <c r="M15" t="n">
-        <v>0.14</v>
+        <v>0.065</v>
       </c>
       <c r="N15" t="n">
-        <v>2.157</v>
+        <v>1.362</v>
       </c>
       <c r="O15" t="n">
-        <v>5.497</v>
+        <v>4.892</v>
       </c>
       <c r="P15" t="n">
-        <v>3.536</v>
+        <v>3.864</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.664999999999999</v>
+        <v>9.474</v>
       </c>
       <c r="R15" t="n">
-        <v>0.158</v>
+        <v>0.372</v>
       </c>
       <c r="S15" t="n">
-        <v>0.275</v>
+        <v>0.36</v>
       </c>
       <c r="T15" t="n">
-        <v>0.251</v>
+        <v>0.187</v>
       </c>
       <c r="U15" t="n">
-        <v>0.183</v>
+        <v>0.059</v>
       </c>
       <c r="V15" t="n">
-        <v>0.08</v>
+        <v>0.015</v>
       </c>
       <c r="W15" t="n">
-        <v>0.053</v>
+        <v>0.006</v>
       </c>
       <c r="X15" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG15" t="n">
         <v>0.026</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.075</v>
-      </c>
       <c r="AH15" t="n">
-        <v>0.052</v>
+        <v>0.017</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.033</v>
+        <v>0.012</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.022</v>
+        <v>0.003</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.629</v>
+        <v>0.45</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.595</v>
+        <v>0.335</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.628</v>
+        <v>0.383</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.612</v>
+        <v>0.405</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.641</v>
+        <v>0.384</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.669</v>
+        <v>0.421</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.426</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.714</v>
+        <v>0.444</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.137</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>824938</v>
+        <v>824859</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2877,145 +2877,145 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t xml:space="preserve">SF </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.702</v>
+        <v>4.294</v>
       </c>
       <c r="G16" t="n">
-        <v>0.427</v>
+        <v>0.481</v>
       </c>
       <c r="H16" t="n">
-        <v>0.094</v>
+        <v>0.097</v>
       </c>
       <c r="I16" t="n">
-        <v>0.212</v>
+        <v>0.255</v>
       </c>
       <c r="J16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.268</v>
+        <v>0.245</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.706</v>
       </c>
       <c r="M16" t="n">
-        <v>0.077</v>
+        <v>0.129</v>
       </c>
       <c r="N16" t="n">
-        <v>1.528</v>
+        <v>1.542</v>
       </c>
       <c r="O16" t="n">
-        <v>5.172</v>
+        <v>5.904</v>
       </c>
       <c r="P16" t="n">
-        <v>3.083</v>
+        <v>3.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.911</v>
+        <v>7.916</v>
       </c>
       <c r="R16" t="n">
-        <v>0.445</v>
+        <v>0.491</v>
       </c>
       <c r="S16" t="n">
-        <v>0.36</v>
+        <v>0.352</v>
       </c>
       <c r="T16" t="n">
-        <v>0.143</v>
+        <v>0.126</v>
       </c>
       <c r="U16" t="n">
-        <v>0.044</v>
+        <v>0.023</v>
       </c>
       <c r="V16" t="n">
         <v>0.007</v>
       </c>
       <c r="W16" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="X16" t="n">
-        <v>0.09</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.143</v>
+        <v>0.105</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.153</v>
+        <v>0.135</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.159</v>
+        <v>0.134</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.124</v>
+        <v>0.121</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.103</v>
+        <v>0.126</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.075</v>
+        <v>0.095</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.047</v>
+        <v>0.079</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="AK16" t="n">
         <v>0.003</v>
       </c>
       <c r="AL16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AM16" t="n">
         <v>0.002</v>
       </c>
-      <c r="AM16" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AN16" t="n">
-        <v>0.389</v>
+        <v>0.53</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.369</v>
+        <v>0.447</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.428</v>
+        <v>0.495</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.358</v>
+        <v>0.431</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.396</v>
+        <v>0.468</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.395</v>
+        <v>0.435</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.389</v>
+        <v>0.411</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.37</v>
+        <v>0.394</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.376</v>
+        <v>0.402</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.138</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="17">
@@ -3043,136 +3043,136 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.127</v>
+        <v>4.147</v>
       </c>
       <c r="G17" t="n">
-        <v>0.468</v>
+        <v>0.459</v>
       </c>
       <c r="H17" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="I17" t="n">
         <v>0.188</v>
       </c>
       <c r="J17" t="n">
-        <v>0.101</v>
+        <v>0.104</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3</v>
+        <v>0.303</v>
       </c>
       <c r="L17" t="n">
-        <v>1.031</v>
+        <v>1.052</v>
       </c>
       <c r="M17" t="n">
-        <v>0.112</v>
+        <v>0.115</v>
       </c>
       <c r="N17" t="n">
-        <v>1.57</v>
+        <v>1.558</v>
       </c>
       <c r="O17" t="n">
-        <v>4.88</v>
+        <v>4.916</v>
       </c>
       <c r="P17" t="n">
-        <v>3.541</v>
+        <v>3.427</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.879</v>
+        <v>8.071999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>0.36</v>
+        <v>0.344</v>
       </c>
       <c r="S17" t="n">
-        <v>0.362</v>
+        <v>0.381</v>
       </c>
       <c r="T17" t="n">
-        <v>0.189</v>
+        <v>0.183</v>
       </c>
       <c r="U17" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="V17" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="W17" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="X17" t="n">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="Z17" t="n">
         <v>0.137</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.152</v>
+        <v>0.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.138</v>
+        <v>0.151</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.133</v>
+        <v>0.117</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.091</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AE17" t="n">
         <v>0.06900000000000001</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="AG17" t="n">
         <v>0.03</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AM17" t="n">
         <v>0.002</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.424</v>
+        <v>0.462</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.45</v>
+        <v>0.443</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.455</v>
+        <v>0.465</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.471</v>
+        <v>0.477</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.461</v>
+        <v>0.483</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.518</v>
+        <v>0.462</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.28</v>
+        <v>0.298</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="18">
@@ -3200,136 +3200,136 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.365</v>
+        <v>4.426</v>
       </c>
       <c r="G18" t="n">
-        <v>0.57</v>
+        <v>0.574</v>
       </c>
       <c r="H18" t="n">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.275</v>
+        <v>0.279</v>
       </c>
       <c r="J18" t="n">
-        <v>0.094</v>
+        <v>0.089</v>
       </c>
       <c r="K18" t="n">
-        <v>0.212</v>
+        <v>0.21</v>
       </c>
       <c r="L18" t="n">
-        <v>1.072</v>
+        <v>1.112</v>
       </c>
       <c r="M18" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="N18" t="n">
-        <v>1.371</v>
+        <v>1.356</v>
       </c>
       <c r="O18" t="n">
-        <v>4.76</v>
+        <v>4.782</v>
       </c>
       <c r="P18" t="n">
-        <v>4.616</v>
+        <v>4.649</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.101000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="R18" t="n">
-        <v>0.339</v>
+        <v>0.324</v>
       </c>
       <c r="S18" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="T18" t="n">
-        <v>0.195</v>
+        <v>0.21</v>
       </c>
       <c r="U18" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="V18" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="W18" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="X18" t="n">
-        <v>0.063</v>
+        <v>0.048</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.093</v>
+        <v>0.105</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.09</v>
+        <v>0.103</v>
       </c>
       <c r="AE18" t="n">
         <v>0.074</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.027</v>
+        <v>0.019</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AM18" t="n">
         <v>0.004</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.527</v>
+        <v>0.515</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.483</v>
+        <v>0.48</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.46</v>
+        <v>0.511</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.484</v>
+        <v>0.477</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.467</v>
+        <v>0.471</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.466</v>
+        <v>0.491</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.498</v>
+        <v>0.508</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.506</v>
+        <v>0.513</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.227</v>
+        <v>0.238</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.141</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="19">
@@ -3357,136 +3357,136 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.775</v>
+        <v>4.543</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="I19" t="n">
-        <v>0.271</v>
+        <v>0.267</v>
       </c>
       <c r="J19" t="n">
-        <v>0.089</v>
+        <v>0.079</v>
       </c>
       <c r="K19" t="n">
-        <v>0.228</v>
+        <v>0.25</v>
       </c>
       <c r="L19" t="n">
-        <v>1.094</v>
+        <v>1.066</v>
       </c>
       <c r="M19" t="n">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="N19" t="n">
-        <v>1.551</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>5.424</v>
+        <v>5.319</v>
       </c>
       <c r="P19" t="n">
-        <v>4.084</v>
+        <v>3.988</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.349</v>
+        <v>7.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.334</v>
+        <v>0.344</v>
       </c>
       <c r="S19" t="n">
-        <v>0.362</v>
+        <v>0.367</v>
       </c>
       <c r="T19" t="n">
-        <v>0.21</v>
+        <v>0.192</v>
       </c>
       <c r="U19" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="V19" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="X19" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.079</v>
+        <v>0.095</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.112</v>
+        <v>0.134</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.141</v>
+        <v>0.147</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.128</v>
+        <v>0.114</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.11</v>
+        <v>0.103</v>
       </c>
       <c r="AE19" t="n">
         <v>0.07199999999999999</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.042</v>
+        <v>0.031</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="AK19" t="n">
         <v>0.007</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.551</v>
+        <v>0.518</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.458</v>
+        <v>0.443</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.519</v>
+        <v>0.505</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.522</v>
+        <v>0.506</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.536</v>
+        <v>0.502</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.542</v>
+        <v>0.49</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.571</v>
+        <v>0.55</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.556</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.283</v>
+        <v>0.239</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="20">
@@ -3514,136 +3514,136 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.785</v>
+        <v>4.711</v>
       </c>
       <c r="G20" t="n">
-        <v>0.642</v>
+        <v>0.647</v>
       </c>
       <c r="H20" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.332</v>
+        <v>0.339</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="K20" t="n">
-        <v>0.175</v>
+        <v>0.187</v>
       </c>
       <c r="L20" t="n">
-        <v>1.139</v>
+        <v>1.077</v>
       </c>
       <c r="M20" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="N20" t="n">
-        <v>1.599</v>
+        <v>1.573</v>
       </c>
       <c r="O20" t="n">
-        <v>4.732</v>
+        <v>4.744</v>
       </c>
       <c r="P20" t="n">
-        <v>4.575</v>
+        <v>4.546</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.373</v>
+        <v>7.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0.329</v>
+        <v>0.336</v>
       </c>
       <c r="S20" t="n">
-        <v>0.353</v>
+        <v>0.369</v>
       </c>
       <c r="T20" t="n">
-        <v>0.209</v>
+        <v>0.202</v>
       </c>
       <c r="U20" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.023</v>
+        <v>0.018</v>
       </c>
       <c r="W20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>0.008</v>
       </c>
-      <c r="X20" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="AK20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.537</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.465</v>
+        <v>0.457</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.548</v>
+        <v>0.532</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.507</v>
+        <v>0.467</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.512</v>
+        <v>0.502</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.574</v>
+        <v>0.579</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.59</v>
+        <v>0.599</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.243</v>
+        <v>0.238</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.116</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="21">
@@ -3671,52 +3671,52 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.582</v>
+        <v>3.687</v>
       </c>
       <c r="G21" t="n">
-        <v>0.428</v>
+        <v>0.421</v>
       </c>
       <c r="H21" t="n">
         <v>0.081</v>
       </c>
       <c r="I21" t="n">
-        <v>0.164</v>
+        <v>0.158</v>
       </c>
       <c r="J21" t="n">
-        <v>0.11</v>
+        <v>0.118</v>
       </c>
       <c r="K21" t="n">
-        <v>0.326</v>
+        <v>0.33</v>
       </c>
       <c r="L21" t="n">
-        <v>1.171</v>
+        <v>1.208</v>
       </c>
       <c r="M21" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="N21" t="n">
-        <v>1.202</v>
+        <v>1.213</v>
       </c>
       <c r="O21" t="n">
-        <v>3.981</v>
+        <v>3.912</v>
       </c>
       <c r="P21" t="n">
-        <v>3.265</v>
+        <v>3.398</v>
       </c>
       <c r="Q21" t="n">
-        <v>10.061</v>
+        <v>10.504</v>
       </c>
       <c r="R21" t="n">
-        <v>0.311</v>
+        <v>0.297</v>
       </c>
       <c r="S21" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="T21" t="n">
-        <v>0.214</v>
+        <v>0.217</v>
       </c>
       <c r="U21" t="n">
-        <v>0.081</v>
+        <v>0.09</v>
       </c>
       <c r="V21" t="n">
         <v>0.028</v>
@@ -3725,46 +3725,46 @@
         <v>0.006</v>
       </c>
       <c r="X21" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.128</v>
+        <v>0.121</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.16</v>
+        <v>0.153</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.144</v>
+        <v>0.135</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.108</v>
+        <v>0.114</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.075</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.052</v>
+        <v>0.058</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AL21" t="n">
         <v>0.001</v>
@@ -3773,34 +3773,34 @@
         <v>0.001</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.303</v>
+        <v>0.316</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.342</v>
+        <v>0.38</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.334</v>
+        <v>0.339</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.376</v>
+        <v>0.351</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.41</v>
+        <v>0.441</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.46</v>
+        <v>0.468</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.46</v>
+        <v>0.471</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.282</v>
+        <v>0.302</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.116</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="22">
@@ -3828,136 +3828,136 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.247</v>
+        <v>4.212</v>
       </c>
       <c r="G22" t="n">
-        <v>0.543</v>
+        <v>0.544</v>
       </c>
       <c r="H22" t="n">
-        <v>0.106</v>
+        <v>0.099</v>
       </c>
       <c r="I22" t="n">
-        <v>0.256</v>
+        <v>0.242</v>
       </c>
       <c r="J22" t="n">
-        <v>0.094</v>
+        <v>0.098</v>
       </c>
       <c r="K22" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="L22" t="n">
-        <v>0.945</v>
+        <v>0.86</v>
       </c>
       <c r="M22" t="n">
-        <v>0.141</v>
+        <v>0.126</v>
       </c>
       <c r="N22" t="n">
-        <v>1.295</v>
+        <v>1.302</v>
       </c>
       <c r="O22" t="n">
-        <v>4.642</v>
+        <v>4.875</v>
       </c>
       <c r="P22" t="n">
-        <v>4.974</v>
+        <v>4.863</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.035</v>
+        <v>9.882999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>0.399</v>
+        <v>0.423</v>
       </c>
       <c r="S22" t="n">
-        <v>0.362</v>
+        <v>0.367</v>
       </c>
       <c r="T22" t="n">
-        <v>0.165</v>
+        <v>0.151</v>
       </c>
       <c r="U22" t="n">
         <v>0.049</v>
       </c>
       <c r="V22" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="X22" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="Y22" t="n">
         <v>0.104</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.142</v>
+        <v>0.144</v>
       </c>
       <c r="AA22" t="n">
         <v>0.148</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.153</v>
+        <v>0.141</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.106</v>
+        <v>0.118</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.044</v>
+        <v>0.051</v>
       </c>
       <c r="AG22" t="n">
         <v>0.034</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AL22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AM22" t="n">
         <v>0.003</v>
       </c>
-      <c r="AM22" t="n">
-        <v>0.005</v>
-      </c>
       <c r="AN22" t="n">
-        <v>0.438</v>
+        <v>0.462</v>
       </c>
       <c r="AO22" t="n">
         <v>0.441</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.421</v>
+        <v>0.399</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.455</v>
+        <v>0.443</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.447</v>
+        <v>0.451</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.499</v>
+        <v>0.486</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.512</v>
+        <v>0.533</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.556</v>
+        <v>0.487</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.25</v>
+        <v>0.268</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.12</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="23">
@@ -3985,16 +3985,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.233</v>
+        <v>4.276</v>
       </c>
       <c r="G23" t="n">
-        <v>0.526</v>
+        <v>0.519</v>
       </c>
       <c r="H23" t="n">
-        <v>0.102</v>
+        <v>0.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.237</v>
+        <v>0.245</v>
       </c>
       <c r="J23" t="n">
         <v>0.097</v>
@@ -4003,76 +4003,76 @@
         <v>0.255</v>
       </c>
       <c r="L23" t="n">
-        <v>0.651</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="N23" t="n">
-        <v>1.661</v>
+        <v>1.606</v>
       </c>
       <c r="O23" t="n">
-        <v>5.263</v>
+        <v>5.261</v>
       </c>
       <c r="P23" t="n">
-        <v>4.52</v>
+        <v>4.466</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.811</v>
+        <v>7.867</v>
       </c>
       <c r="R23" t="n">
-        <v>0.527</v>
+        <v>0.503</v>
       </c>
       <c r="S23" t="n">
-        <v>0.328</v>
+        <v>0.344</v>
       </c>
       <c r="T23" t="n">
-        <v>0.115</v>
+        <v>0.123</v>
       </c>
       <c r="U23" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="V23" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="X23" t="n">
-        <v>0.066</v>
+        <v>0.068</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1</v>
+        <v>0.109</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.136</v>
+        <v>0.129</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.152</v>
+        <v>0.146</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.14</v>
+        <v>0.132</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.119</v>
+        <v>0.111</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.091</v>
+        <v>0.096</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.048</v>
+        <v>0.055</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AJ23" t="n">
         <v>0.006</v>
@@ -4087,34 +4087,34 @@
         <v>0.003</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.493</v>
+        <v>0.523</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.433</v>
+        <v>0.43</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.463</v>
+        <v>0.456</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.448</v>
+        <v>0.445</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.471</v>
+        <v>0.461</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.474</v>
+        <v>0.461</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.464</v>
+        <v>0.521</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.478</v>
+        <v>0.492</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.261</v>
+        <v>0.257</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.127</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="24">
@@ -4142,52 +4142,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.506</v>
+        <v>3.546</v>
       </c>
       <c r="G24" t="n">
-        <v>0.405</v>
+        <v>0.418</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="I24" t="n">
-        <v>0.153</v>
+        <v>0.163</v>
       </c>
       <c r="J24" t="n">
-        <v>0.119</v>
+        <v>0.122</v>
       </c>
       <c r="K24" t="n">
-        <v>0.349</v>
+        <v>0.319</v>
       </c>
       <c r="L24" t="n">
-        <v>0.632</v>
+        <v>0.671</v>
       </c>
       <c r="M24" t="n">
-        <v>0.082</v>
+        <v>0.097</v>
       </c>
       <c r="N24" t="n">
-        <v>1.604</v>
+        <v>1.586</v>
       </c>
       <c r="O24" t="n">
-        <v>4.991</v>
+        <v>4.747</v>
       </c>
       <c r="P24" t="n">
-        <v>2.992</v>
+        <v>3.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.497</v>
+        <v>8.853999999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>0.526</v>
+        <v>0.518</v>
       </c>
       <c r="S24" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="T24" t="n">
-        <v>0.095</v>
+        <v>0.118</v>
       </c>
       <c r="U24" t="n">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
       <c r="V24" t="n">
         <v>0.004</v>
@@ -4196,40 +4196,40 @@
         <v>0.001</v>
       </c>
       <c r="X24" t="n">
-        <v>0.093</v>
+        <v>0.097</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.148</v>
+        <v>0.142</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.165</v>
+        <v>0.167</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.162</v>
+        <v>0.151</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.126</v>
+        <v>0.132</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.105</v>
+        <v>0.101</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.073</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.051</v>
+        <v>0.048</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.036</v>
+        <v>0.027</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AJ24" t="n">
         <v>0.004</v>
@@ -4238,40 +4238,40 @@
         <v>0.002</v>
       </c>
       <c r="AL24" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AM24" t="n">
         <v>0.001</v>
       </c>
-      <c r="AM24" t="n">
-        <v>0.002</v>
-      </c>
       <c r="AN24" t="n">
-        <v>0.35</v>
+        <v>0.379</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.324</v>
+        <v>0.332</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.362</v>
+        <v>0.316</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.336</v>
+        <v>0.339</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.357</v>
+        <v>0.347</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.388</v>
+        <v>0.374</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.446</v>
+        <v>0.438</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.478</v>
+        <v>0.538</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.12</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="25">
@@ -4299,136 +4299,136 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.279</v>
+        <v>4.383</v>
       </c>
       <c r="G25" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="H25" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.228</v>
+        <v>0.233</v>
       </c>
       <c r="J25" t="n">
-        <v>0.102</v>
+        <v>0.113</v>
       </c>
       <c r="K25" t="n">
-        <v>0.302</v>
+        <v>0.294</v>
       </c>
       <c r="L25" t="n">
-        <v>0.821</v>
+        <v>0.879</v>
       </c>
       <c r="M25" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
       <c r="N25" t="n">
-        <v>1.776</v>
+        <v>1.76</v>
       </c>
       <c r="O25" t="n">
-        <v>4.95</v>
+        <v>5.018</v>
       </c>
       <c r="P25" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.438</v>
+        <v>7.104</v>
       </c>
       <c r="R25" t="n">
-        <v>0.446</v>
+        <v>0.432</v>
       </c>
       <c r="S25" t="n">
-        <v>0.358</v>
+        <v>0.348</v>
       </c>
       <c r="T25" t="n">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="U25" t="n">
-        <v>0.04</v>
+        <v>0.053</v>
       </c>
       <c r="V25" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="W25" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="X25" t="n">
-        <v>0.057</v>
+        <v>0.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.115</v>
+        <v>0.094</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.134</v>
+        <v>0.138</v>
       </c>
       <c r="AA25" t="n">
         <v>0.144</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.119</v>
+        <v>0.114</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.065</v>
+        <v>0.073</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.057</v>
+        <v>0.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="AI25" t="n">
         <v>0.015</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.471</v>
+        <v>0.487</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.548</v>
+        <v>0.516</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.496</v>
+        <v>0.52</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.502</v>
+        <v>0.516</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.444</v>
+        <v>0.493</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.458</v>
+        <v>0.407</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.406</v>
+        <v>0.424</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.192</v>
+        <v>0.211</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="26">
@@ -4456,136 +4456,136 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.278</v>
+        <v>4.62</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.711</v>
       </c>
       <c r="H26" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="I26" t="n">
-        <v>0.354</v>
+        <v>0.378</v>
       </c>
       <c r="J26" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K26" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5.913</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6.854</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.118</v>
       </c>
-      <c r="L26" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.314</v>
-      </c>
-      <c r="O26" t="n">
-        <v>5.759</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.169</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.742</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0.053</v>
       </c>
-      <c r="Y26" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0.044</v>
-      </c>
       <c r="AG26" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="AI26" t="n">
         <v>0.013</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="AL26" t="n">
         <v>0.004</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.483</v>
+        <v>0.547</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.46</v>
+        <v>0.491</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.473</v>
+        <v>0.476</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.458</v>
+        <v>0.462</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.485</v>
+        <v>0.497</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.524</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.466</v>
+        <v>0.594</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.534</v>
+        <v>0.579</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.179</v>
+        <v>0.184</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.122</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="27">
@@ -4613,94 +4613,94 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.749</v>
+        <v>3.59</v>
       </c>
       <c r="G27" t="n">
-        <v>0.591</v>
+        <v>0.574</v>
       </c>
       <c r="H27" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="I27" t="n">
-        <v>0.257</v>
+        <v>0.245</v>
       </c>
       <c r="J27" t="n">
-        <v>0.094</v>
+        <v>0.107</v>
       </c>
       <c r="K27" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="L27" t="n">
-        <v>0.804</v>
+        <v>0.768</v>
       </c>
       <c r="M27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="N27" t="n">
-        <v>1.421</v>
+        <v>1.35</v>
       </c>
       <c r="O27" t="n">
-        <v>4.804</v>
+        <v>4.82</v>
       </c>
       <c r="P27" t="n">
-        <v>3.873</v>
+        <v>3.662</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.894</v>
+        <v>7.741</v>
       </c>
       <c r="R27" t="n">
-        <v>0.446</v>
+        <v>0.458</v>
       </c>
       <c r="S27" t="n">
-        <v>0.36</v>
+        <v>0.367</v>
       </c>
       <c r="T27" t="n">
-        <v>0.147</v>
+        <v>0.133</v>
       </c>
       <c r="U27" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="V27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="W27" t="n">
         <v>0.001</v>
       </c>
       <c r="X27" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.076</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.08</v>
       </c>
       <c r="AE27" t="n">
         <v>0.053</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AJ27" t="n">
         <v>0.005</v>
@@ -4709,40 +4709,40 @@
         <v>0.002</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AM27" t="n">
         <v>0.001</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.437</v>
+        <v>0.388</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.381</v>
+        <v>0.397</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.426</v>
+        <v>0.385</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.392</v>
+        <v>0.377</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.422</v>
+        <v>0.384</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.451</v>
+        <v>0.405</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.447</v>
+        <v>0.416</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.189</v>
+        <v>0.203</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.107</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="28">
@@ -4770,136 +4770,136 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.549</v>
+        <v>5.326</v>
       </c>
       <c r="G28" t="n">
-        <v>0.651</v>
+        <v>0.627</v>
       </c>
       <c r="H28" t="n">
-        <v>0.122</v>
+        <v>0.107</v>
       </c>
       <c r="I28" t="n">
-        <v>0.354</v>
+        <v>0.338</v>
       </c>
       <c r="J28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.185</v>
+        <v>0.174</v>
       </c>
       <c r="L28" t="n">
-        <v>1.328</v>
+        <v>1.276</v>
       </c>
       <c r="M28" t="n">
-        <v>0.135</v>
+        <v>0.15</v>
       </c>
       <c r="N28" t="n">
-        <v>1.463</v>
+        <v>1.486</v>
       </c>
       <c r="O28" t="n">
-        <v>5.004</v>
+        <v>4.979</v>
       </c>
       <c r="P28" t="n">
-        <v>5.499</v>
+        <v>5.047</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.547</v>
+        <v>7.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0.265</v>
+        <v>0.266</v>
       </c>
       <c r="S28" t="n">
-        <v>0.354</v>
+        <v>0.363</v>
       </c>
       <c r="T28" t="n">
-        <v>0.227</v>
+        <v>0.245</v>
       </c>
       <c r="U28" t="n">
-        <v>0.106</v>
+        <v>0.091</v>
       </c>
       <c r="V28" t="n">
-        <v>0.037</v>
+        <v>0.026</v>
       </c>
       <c r="W28" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="X28" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.116</v>
+        <v>0.121</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.13</v>
+        <v>0.143</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.123</v>
+        <v>0.129</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.091</v>
+        <v>0.098</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.077</v>
+        <v>0.064</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="AH28" t="n">
         <v>0.036</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="AK28" t="n">
         <v>0.012</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.508</v>
+        <v>0.52</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.593</v>
+        <v>0.549</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.616</v>
+        <v>0.637</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.662</v>
+        <v>0.61</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.667</v>
+        <v>0.594</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.632</v>
+        <v>0.645</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.674</v>
+        <v>0.648</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.25</v>
+        <v>0.249</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="29">
@@ -4927,88 +4927,88 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.63</v>
+        <v>3.586</v>
       </c>
       <c r="G29" t="n">
-        <v>0.554</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="I29" t="n">
-        <v>0.238</v>
+        <v>0.239</v>
       </c>
       <c r="J29" t="n">
-        <v>0.095</v>
+        <v>0.1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.215</v>
+        <v>0.194</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.666</v>
       </c>
       <c r="M29" t="n">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="N29" t="n">
-        <v>1.376</v>
+        <v>1.399</v>
       </c>
       <c r="O29" t="n">
-        <v>4.802</v>
+        <v>4.911</v>
       </c>
       <c r="P29" t="n">
-        <v>3.478</v>
+        <v>3.278</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.808</v>
+        <v>6.57</v>
       </c>
       <c r="R29" t="n">
-        <v>0.503</v>
+        <v>0.513</v>
       </c>
       <c r="S29" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="T29" t="n">
-        <v>0.121</v>
+        <v>0.112</v>
       </c>
       <c r="U29" t="n">
         <v>0.026</v>
       </c>
       <c r="V29" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="W29" t="n">
         <v>0.001</v>
       </c>
       <c r="X29" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.162</v>
+        <v>0.157</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.154</v>
+        <v>0.165</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.149</v>
+        <v>0.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.102</v>
+        <v>0.106</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.082</v>
+        <v>0.077</v>
       </c>
       <c r="AE29" t="n">
         <v>0.049</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="AH29" t="n">
         <v>0.01</v>
@@ -5020,7 +5020,7 @@
         <v>0.005</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AL29" t="n">
         <v>0.002</v>
@@ -5029,34 +5029,34 @@
         <v>0.001</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.364</v>
+        <v>0.382</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.347</v>
+        <v>0.377</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.371</v>
+        <v>0.353</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.364</v>
+        <v>0.378</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.44</v>
+        <v>0.413</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.451</v>
+        <v>0.403</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.46</v>
+        <v>0.466</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.215</v>
+        <v>0.217</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="30">
@@ -5084,136 +5084,136 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6.566</v>
+        <v>6.238</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="I30" t="n">
-        <v>0.315</v>
+        <v>0.304</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="K30" t="n">
-        <v>0.281</v>
+        <v>0.282</v>
       </c>
       <c r="L30" t="n">
-        <v>1.792</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0.134</v>
+        <v>0.143</v>
       </c>
       <c r="N30" t="n">
-        <v>1.698</v>
+        <v>1.74</v>
       </c>
       <c r="O30" t="n">
-        <v>5.538</v>
+        <v>5.184</v>
       </c>
       <c r="P30" t="n">
-        <v>5.63</v>
+        <v>5.449</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.628</v>
+        <v>9.683999999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>0.175</v>
+        <v>0.187</v>
       </c>
       <c r="S30" t="n">
-        <v>0.298</v>
+        <v>0.307</v>
       </c>
       <c r="T30" t="n">
-        <v>0.253</v>
+        <v>0.265</v>
       </c>
       <c r="U30" t="n">
-        <v>0.164</v>
+        <v>0.144</v>
       </c>
       <c r="V30" t="n">
-        <v>0.068</v>
+        <v>0.064</v>
       </c>
       <c r="W30" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="X30" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="Z30" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.063</v>
       </c>
-      <c r="AA30" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0.068</v>
-      </c>
       <c r="AH30" t="n">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.715</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.642</v>
+        <v>0.619</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.669</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.725</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.76</v>
+        <v>0.672</v>
       </c>
       <c r="AS30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT30" t="n">
         <v>0.782</v>
       </c>
-      <c r="AT30" t="n">
-        <v>0.764</v>
-      </c>
       <c r="AU30" t="n">
-        <v>0.844</v>
+        <v>0.777</v>
       </c>
       <c r="AV30" t="n">
         <v>0.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="31">
@@ -5241,55 +5241,55 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.074</v>
+        <v>4.101</v>
       </c>
       <c r="G31" t="n">
-        <v>0.573</v>
+        <v>0.57</v>
       </c>
       <c r="H31" t="n">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
       <c r="I31" t="n">
-        <v>0.268</v>
+        <v>0.273</v>
       </c>
       <c r="J31" t="n">
-        <v>0.094</v>
+        <v>0.095</v>
       </c>
       <c r="K31" t="n">
-        <v>0.212</v>
+        <v>0.21</v>
       </c>
       <c r="L31" t="n">
-        <v>0.958</v>
+        <v>0.91</v>
       </c>
       <c r="M31" t="n">
-        <v>0.137</v>
+        <v>0.127</v>
       </c>
       <c r="N31" t="n">
-        <v>1.64</v>
+        <v>1.688</v>
       </c>
       <c r="O31" t="n">
-        <v>4.735</v>
+        <v>4.819</v>
       </c>
       <c r="P31" t="n">
-        <v>3.315</v>
+        <v>3.449</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.93</v>
+        <v>7.812</v>
       </c>
       <c r="R31" t="n">
-        <v>0.374</v>
+        <v>0.405</v>
       </c>
       <c r="S31" t="n">
-        <v>0.381</v>
+        <v>0.358</v>
       </c>
       <c r="T31" t="n">
-        <v>0.176</v>
+        <v>0.171</v>
       </c>
       <c r="U31" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="V31" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="W31" t="n">
         <v>0.002</v>
@@ -5298,79 +5298,79 @@
         <v>0.063</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.132</v>
+        <v>0.146</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.155</v>
+        <v>0.147</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.158</v>
+        <v>0.141</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.114</v>
+        <v>0.119</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.075</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.007</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AM31" t="n">
         <v>0.002</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.481</v>
+        <v>0.491</v>
       </c>
       <c r="AO31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="AT31" t="n">
         <v>0.458</v>
       </c>
-      <c r="AP31" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.425</v>
-      </c>
       <c r="AU31" t="n">
-        <v>0.481</v>
+        <v>0.431</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.209</v>
+        <v>0.186</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
     </row>
   </sheetData>

--- a/data/live/BallparkPal_Teams_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Teams_2026-04-12.xlsx
@@ -1630,136 +1630,136 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.907</v>
+        <v>5.675</v>
       </c>
       <c r="G8" t="n">
-        <v>0.456</v>
+        <v>0.484</v>
       </c>
       <c r="H8" t="n">
-        <v>0.078</v>
+        <v>0.095</v>
       </c>
       <c r="I8" t="n">
-        <v>0.282</v>
+        <v>0.277</v>
       </c>
       <c r="J8" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.697</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.458</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.523</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.091</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.815</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="AA8" t="n">
         <v>0.122</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5.318</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.395</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.606999999999999</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.096</v>
-      </c>
       <c r="AB8" t="n">
-        <v>0.119</v>
+        <v>0.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.119</v>
+        <v>0.111</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.104</v>
+        <v>0.1</v>
       </c>
       <c r="AE8" t="n">
         <v>0.103</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.061</v>
+        <v>0.057</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.041</v>
+        <v>0.049</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.034</v>
+        <v>0.029</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.609</v>
+        <v>0.606</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.606</v>
+        <v>0.584</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.606</v>
+        <v>0.591</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.609</v>
+        <v>0.551</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.606</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.626</v>
+        <v>0.631</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.658</v>
+        <v>0.598</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.617</v>
+        <v>0.613</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.68</v>
+        <v>0.661</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.159</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="9">
@@ -5084,136 +5084,136 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6.238</v>
+        <v>5.776</v>
       </c>
       <c r="G30" t="n">
-        <v>0.544</v>
+        <v>0.516</v>
       </c>
       <c r="H30" t="n">
-        <v>0.091</v>
+        <v>0.093</v>
       </c>
       <c r="I30" t="n">
-        <v>0.304</v>
+        <v>0.277</v>
       </c>
       <c r="J30" t="n">
-        <v>0.078</v>
+        <v>0.095</v>
       </c>
       <c r="K30" t="n">
-        <v>0.282</v>
+        <v>0.277</v>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>1.453</v>
       </c>
       <c r="M30" t="n">
-        <v>0.143</v>
+        <v>0.129</v>
       </c>
       <c r="N30" t="n">
-        <v>1.74</v>
+        <v>1.695</v>
       </c>
       <c r="O30" t="n">
-        <v>5.184</v>
+        <v>5.325</v>
       </c>
       <c r="P30" t="n">
-        <v>5.449</v>
+        <v>5.369</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.683999999999999</v>
+        <v>9.782</v>
       </c>
       <c r="R30" t="n">
-        <v>0.187</v>
+        <v>0.229</v>
       </c>
       <c r="S30" t="n">
-        <v>0.307</v>
+        <v>0.346</v>
       </c>
       <c r="T30" t="n">
-        <v>0.265</v>
+        <v>0.244</v>
       </c>
       <c r="U30" t="n">
-        <v>0.144</v>
+        <v>0.124</v>
       </c>
       <c r="V30" t="n">
-        <v>0.064</v>
+        <v>0.04</v>
       </c>
       <c r="W30" t="n">
-        <v>0.032</v>
+        <v>0.017</v>
       </c>
       <c r="X30" t="n">
-        <v>0.018</v>
+        <v>0.026</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.104</v>
+        <v>0.101</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.124</v>
+        <v>0.12</v>
       </c>
       <c r="AC30" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AD30" t="n">
         <v>0.117</v>
       </c>
-      <c r="AD30" t="n">
-        <v>0.105</v>
-      </c>
       <c r="AE30" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="AG30" t="n">
         <v>0.063</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.051</v>
+        <v>0.043</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.035</v>
+        <v>0.028</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.03</v>
+        <v>0.018</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.592</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.619</v>
+        <v>0.587</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.669</v>
+        <v>0.608</v>
       </c>
       <c r="AQ30" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="AT30" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="AR30" t="n">
-        <v>0.672</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.782</v>
-      </c>
       <c r="AU30" t="n">
-        <v>0.777</v>
+        <v>0.742</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.107</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="31">

--- a/data/live/BallparkPal_Teams_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Teams_2026-04-12.xlsx
@@ -665,7 +665,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>822998</v>
+        <v>822828</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -679,150 +679,150 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB </t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.505</v>
+        <v>4.593</v>
       </c>
       <c r="G2" t="n">
-        <v>0.582</v>
+        <v>0.54</v>
       </c>
       <c r="H2" t="n">
-        <v>0.122</v>
+        <v>0.096</v>
       </c>
       <c r="I2" t="n">
-        <v>0.319</v>
+        <v>0.302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.082</v>
+        <v>0.097</v>
       </c>
       <c r="K2" t="n">
-        <v>0.163</v>
+        <v>0.175</v>
       </c>
       <c r="L2" t="n">
-        <v>1.385</v>
+        <v>1.483</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12</v>
+        <v>0.075</v>
       </c>
       <c r="N2" t="n">
-        <v>1.501</v>
+        <v>1.664</v>
       </c>
       <c r="O2" t="n">
-        <v>4.503</v>
+        <v>4.777</v>
       </c>
       <c r="P2" t="n">
-        <v>3.662</v>
+        <v>3.362</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.246</v>
+        <v>9.083</v>
       </c>
       <c r="R2" t="n">
-        <v>0.272</v>
+        <v>0.216</v>
       </c>
       <c r="S2" t="n">
-        <v>0.33</v>
+        <v>0.352</v>
       </c>
       <c r="T2" t="n">
-        <v>0.222</v>
+        <v>0.254</v>
       </c>
       <c r="U2" t="n">
-        <v>0.117</v>
+        <v>0.113</v>
       </c>
       <c r="V2" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.043</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.05</v>
-      </c>
       <c r="Y2" t="n">
-        <v>0.097</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="AA2" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0.138</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.119</v>
-      </c>
       <c r="AD2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.08</v>
+        <v>0.074</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AM2" t="n">
         <v>0.004</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.504</v>
+        <v>0.579</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.385</v>
+        <v>0.539</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.456</v>
+        <v>0.578</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.457</v>
+        <v>0.553</v>
       </c>
       <c r="AR2" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0.431</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0.501</v>
-      </c>
       <c r="AT2" t="n">
-        <v>0.489</v>
+        <v>0.404</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.513</v>
+        <v>0.398</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.514</v>
+        <v>0.348</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.158</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>823075</v>
+        <v>823154</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -836,150 +836,150 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.705</v>
+        <v>3.941</v>
       </c>
       <c r="G3" t="n">
-        <v>0.533</v>
+        <v>0.426</v>
       </c>
       <c r="H3" t="n">
-        <v>0.113</v>
+        <v>0.089</v>
       </c>
       <c r="I3" t="n">
-        <v>0.294</v>
+        <v>0.21</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="K3" t="n">
-        <v>0.233</v>
+        <v>0.279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.857</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.161</v>
+        <v>0.075</v>
       </c>
       <c r="N3" t="n">
-        <v>1.787</v>
+        <v>1.426</v>
       </c>
       <c r="O3" t="n">
-        <v>5.603</v>
+        <v>5.015</v>
       </c>
       <c r="P3" t="n">
-        <v>4.126</v>
+        <v>2.576</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.029</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.427</v>
+        <v>0.289</v>
       </c>
       <c r="S3" t="n">
-        <v>0.357</v>
+        <v>0.363</v>
       </c>
       <c r="T3" t="n">
-        <v>0.161</v>
+        <v>0.22</v>
       </c>
       <c r="U3" t="n">
-        <v>0.044</v>
+        <v>0.09</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008</v>
+        <v>0.027</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="X3" t="n">
-        <v>0.049</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.093</v>
+        <v>0.126</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.115</v>
+        <v>0.143</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.138</v>
+        <v>0.155</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.132</v>
+        <v>0.143</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.114</v>
+        <v>0.102</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.104</v>
+        <v>0.091</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.081</v>
+        <v>0.057</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.063</v>
+        <v>0.046</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.042</v>
+        <v>0.025</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.027</v>
+        <v>0.015</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AL3" t="n">
         <v>0.002</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.543</v>
+        <v>0.431</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.491</v>
+        <v>0.386</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.535</v>
+        <v>0.392</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.543</v>
+        <v>0.391</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.478</v>
+        <v>0.385</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.491</v>
+        <v>0.419</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.457</v>
+        <v>0.434</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.438</v>
+        <v>0.419</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.441</v>
+        <v>0.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.149</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>823317</v>
+        <v>823479</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -993,150 +993,150 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD </t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.892</v>
+        <v>4.257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.289</v>
+        <v>0.436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="I4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.113</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.137</v>
-      </c>
       <c r="K4" t="n">
-        <v>0.378</v>
+        <v>0.267</v>
       </c>
       <c r="L4" t="n">
-        <v>0.951</v>
+        <v>0.822</v>
       </c>
       <c r="M4" t="n">
-        <v>0.095</v>
+        <v>0.152</v>
       </c>
       <c r="N4" t="n">
-        <v>0.946</v>
+        <v>1.44</v>
       </c>
       <c r="O4" t="n">
-        <v>3.938</v>
+        <v>6.048</v>
       </c>
       <c r="P4" t="n">
-        <v>2.857</v>
+        <v>3.532</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.654</v>
+        <v>7.845</v>
       </c>
       <c r="R4" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="AO4" t="n">
         <v>0.396</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.256</v>
-      </c>
       <c r="AP4" t="n">
-        <v>0.287</v>
+        <v>0.485</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.258</v>
+        <v>0.435</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.302</v>
+        <v>0.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.312</v>
+        <v>0.477</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.332</v>
+        <v>0.43</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.334</v>
+        <v>0.433</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.34</v>
+        <v>0.415</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>823642</v>
+        <v>823804</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1150,150 +1150,150 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.23</v>
+        <v>3.667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.426</v>
+        <v>0.372</v>
       </c>
       <c r="H5" t="n">
-        <v>0.107</v>
+        <v>0.076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.184</v>
+        <v>0.179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.121</v>
+        <v>0.129</v>
       </c>
       <c r="K5" t="n">
-        <v>0.245</v>
+        <v>0.326</v>
       </c>
       <c r="L5" t="n">
-        <v>0.716</v>
+        <v>1.012</v>
       </c>
       <c r="M5" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.784</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.879</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9.087</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X5" t="n">
         <v>0.097</v>
       </c>
-      <c r="N5" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.378</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.002</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>11.929</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.113</v>
-      </c>
       <c r="Y5" t="n">
-        <v>0.172</v>
+        <v>0.138</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.176</v>
+        <v>0.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.147</v>
+        <v>0.163</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.096</v>
+        <v>0.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.06</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AE5" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0.041</v>
       </c>
-      <c r="AF5" t="n">
-        <v>0.027</v>
-      </c>
       <c r="AG5" t="n">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="AI5" t="n">
         <v>0.006</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="AK5" t="n">
         <v>0.003</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.366</v>
+        <v>0.399</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.294</v>
+        <v>0.362</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.327</v>
+        <v>0.382</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.292</v>
+        <v>0.365</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.325</v>
+        <v>0.355</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.365</v>
+        <v>0.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.349</v>
+        <v>0.359</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.341</v>
+        <v>0.438</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.34</v>
+        <v>0.389</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.145</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>824126</v>
+        <v>823966</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1307,150 +1307,150 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHW</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC </t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.254</v>
+        <v>4.783</v>
       </c>
       <c r="G6" t="n">
-        <v>0.373</v>
+        <v>0.579</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="I6" t="n">
-        <v>0.174</v>
+        <v>0.33</v>
       </c>
       <c r="J6" t="n">
-        <v>0.107</v>
+        <v>0.081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.338</v>
+        <v>0.158</v>
       </c>
       <c r="L6" t="n">
-        <v>1.134</v>
+        <v>1.201</v>
       </c>
       <c r="M6" t="n">
-        <v>0.045</v>
+        <v>0.111</v>
       </c>
       <c r="N6" t="n">
-        <v>1.533</v>
+        <v>1.606</v>
       </c>
       <c r="O6" t="n">
-        <v>4.987</v>
+        <v>4.792</v>
       </c>
       <c r="P6" t="n">
-        <v>3.38</v>
+        <v>4.908</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.715</v>
+        <v>8.997999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>0.322</v>
+        <v>0.304</v>
       </c>
       <c r="S6" t="n">
-        <v>0.363</v>
+        <v>0.369</v>
       </c>
       <c r="T6" t="n">
-        <v>0.21</v>
+        <v>0.197</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08</v>
+        <v>0.093</v>
       </c>
       <c r="V6" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="X6" t="n">
-        <v>0.062</v>
+        <v>0.041</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.106</v>
+        <v>0.091</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.133</v>
+        <v>0.122</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.149</v>
+        <v>0.137</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.137</v>
+        <v>0.141</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.118</v>
+        <v>0.114</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.066</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.033</v>
+        <v>0.042</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AL6" t="n">
         <v>0.005</v>
       </c>
-      <c r="AK6" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.003</v>
-      </c>
       <c r="AM6" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.513</v>
+        <v>0.585</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.442</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.437</v>
+        <v>0.526</v>
       </c>
       <c r="AR6" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AT6" t="n">
         <v>0.457</v>
       </c>
-      <c r="AS6" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0.432</v>
       </c>
-      <c r="AU6" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.391</v>
-      </c>
       <c r="AW6" t="n">
-        <v>0.128</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>824293</v>
+        <v>824533</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1464,150 +1464,150 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.227</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>0.433</v>
+        <v>0.456</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="I7" t="n">
-        <v>0.194</v>
+        <v>0.22</v>
       </c>
       <c r="J7" t="n">
-        <v>0.125</v>
+        <v>0.099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.239</v>
+        <v>0.242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.578</v>
+        <v>1.004</v>
       </c>
       <c r="M7" t="n">
-        <v>0.151</v>
+        <v>0.065</v>
       </c>
       <c r="N7" t="n">
-        <v>1.426</v>
+        <v>1.362</v>
       </c>
       <c r="O7" t="n">
-        <v>5.16</v>
+        <v>4.892</v>
       </c>
       <c r="P7" t="n">
-        <v>2.375</v>
+        <v>3.864</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.165</v>
+        <v>9.474</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.372</v>
       </c>
       <c r="S7" t="n">
-        <v>0.325</v>
+        <v>0.36</v>
       </c>
       <c r="T7" t="n">
-        <v>0.095</v>
+        <v>0.187</v>
       </c>
       <c r="U7" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.015</v>
       </c>
-      <c r="V7" t="n">
-        <v>0.004</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="X7" t="n">
-        <v>0.126</v>
+        <v>0.074</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.166</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.171</v>
+        <v>0.154</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.144</v>
+        <v>0.153</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.124</v>
+        <v>0.138</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.046</v>
+        <v>0.068</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.321</v>
+        <v>0.45</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.266</v>
+        <v>0.335</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.294</v>
+        <v>0.383</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.305</v>
+        <v>0.405</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.292</v>
+        <v>0.384</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.346</v>
+        <v>0.421</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.348</v>
+        <v>0.426</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.397</v>
+        <v>0.444</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.404</v>
+        <v>0.436</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.159</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>824696</v>
+        <v>824859</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1621,150 +1621,150 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t xml:space="preserve">SF </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.675</v>
+        <v>4.255</v>
       </c>
       <c r="G8" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.599</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.655</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.879</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.887</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>0.484</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.697</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.135</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5.458</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.415</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.523</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.551</v>
-      </c>
       <c r="AR8" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.446</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.631</v>
+        <v>0.399</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.598</v>
+        <v>0.395</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.613</v>
+        <v>0.399</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.661</v>
+        <v>0.385</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.17</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>824938</v>
+        <v>822998</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1778,150 +1778,150 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t xml:space="preserve">TB </t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.666</v>
+        <v>4.505</v>
       </c>
       <c r="G9" t="n">
-        <v>0.43</v>
+        <v>0.582</v>
       </c>
       <c r="H9" t="n">
-        <v>0.095</v>
+        <v>0.122</v>
       </c>
       <c r="I9" t="n">
-        <v>0.21</v>
+        <v>0.319</v>
       </c>
       <c r="J9" t="n">
-        <v>0.113</v>
+        <v>0.082</v>
       </c>
       <c r="K9" t="n">
-        <v>0.273</v>
+        <v>0.163</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.385</v>
       </c>
       <c r="M9" t="n">
-        <v>0.066</v>
+        <v>0.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.59</v>
+        <v>1.501</v>
       </c>
       <c r="O9" t="n">
-        <v>5.101</v>
+        <v>4.503</v>
       </c>
       <c r="P9" t="n">
-        <v>3.084</v>
+        <v>3.662</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.027</v>
+        <v>9.246</v>
       </c>
       <c r="R9" t="n">
-        <v>0.451</v>
+        <v>0.272</v>
       </c>
       <c r="S9" t="n">
-        <v>0.352</v>
+        <v>0.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0.142</v>
+        <v>0.222</v>
       </c>
       <c r="U9" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="V9" t="n">
         <v>0.043</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>0.01</v>
       </c>
-      <c r="W9" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.003</v>
-      </c>
       <c r="AK9" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.421</v>
+        <v>0.504</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.348</v>
+        <v>0.385</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.405</v>
+        <v>0.456</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.36</v>
+        <v>0.457</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.39</v>
+        <v>0.431</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.387</v>
+        <v>0.501</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.4</v>
+        <v>0.489</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.367</v>
+        <v>0.513</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.356</v>
+        <v>0.514</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.142</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>822828</v>
+        <v>823075</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1935,100 +1935,100 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.793</v>
+        <v>4.705</v>
       </c>
       <c r="G10" t="n">
-        <v>0.541</v>
+        <v>0.533</v>
       </c>
       <c r="H10" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.787</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.603</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.126</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.029</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AD10" t="n">
         <v>0.104</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.501</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.871</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.506</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8.977</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.108</v>
-      </c>
       <c r="AE10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="AI10" t="n">
         <v>0.016</v>
@@ -2037,48 +2037,48 @@
         <v>0.011</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.616</v>
+        <v>0.543</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.547</v>
+        <v>0.491</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.593</v>
+        <v>0.535</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.543</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.511</v>
+        <v>0.478</v>
       </c>
       <c r="AS10" t="n">
         <v>0.491</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.432</v>
+        <v>0.457</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.418</v>
+        <v>0.438</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.404</v>
+        <v>0.441</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.125</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>823154</v>
+        <v>823317</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2092,150 +2092,150 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t xml:space="preserve">SD </t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.941</v>
+        <v>2.892</v>
       </c>
       <c r="G11" t="n">
-        <v>0.426</v>
+        <v>0.289</v>
       </c>
       <c r="H11" t="n">
-        <v>0.089</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.21</v>
+        <v>0.113</v>
       </c>
       <c r="J11" t="n">
-        <v>0.11</v>
+        <v>0.137</v>
       </c>
       <c r="K11" t="n">
-        <v>0.279</v>
+        <v>0.378</v>
       </c>
       <c r="L11" t="n">
-        <v>1.24</v>
+        <v>0.951</v>
       </c>
       <c r="M11" t="n">
-        <v>0.075</v>
+        <v>0.095</v>
       </c>
       <c r="N11" t="n">
-        <v>1.426</v>
+        <v>0.946</v>
       </c>
       <c r="O11" t="n">
-        <v>5.015</v>
+        <v>3.938</v>
       </c>
       <c r="P11" t="n">
-        <v>2.576</v>
+        <v>2.857</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.553000000000001</v>
+        <v>11.654</v>
       </c>
       <c r="R11" t="n">
-        <v>0.289</v>
+        <v>0.396</v>
       </c>
       <c r="S11" t="n">
-        <v>0.363</v>
+        <v>0.355</v>
       </c>
       <c r="T11" t="n">
-        <v>0.22</v>
+        <v>0.177</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09</v>
+        <v>0.054</v>
       </c>
       <c r="V11" t="n">
-        <v>0.027</v>
+        <v>0.014</v>
       </c>
       <c r="W11" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="X11" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.126</v>
+        <v>0.179</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.143</v>
+        <v>0.187</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.143</v>
+        <v>0.12</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.102</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.091</v>
+        <v>0.053</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.057</v>
+        <v>0.041</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.046</v>
+        <v>0.022</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
         <v>0.001</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.431</v>
+        <v>0.318</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.386</v>
+        <v>0.256</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.392</v>
+        <v>0.287</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.391</v>
+        <v>0.258</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.385</v>
+        <v>0.302</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.419</v>
+        <v>0.312</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.434</v>
+        <v>0.332</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.419</v>
+        <v>0.334</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.156</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>823479</v>
+        <v>823642</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2249,150 +2249,150 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.257</v>
+        <v>3.23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.436</v>
+        <v>0.426</v>
       </c>
       <c r="H12" t="n">
-        <v>0.079</v>
+        <v>0.107</v>
       </c>
       <c r="I12" t="n">
-        <v>0.25</v>
+        <v>0.184</v>
       </c>
       <c r="J12" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.378</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.002</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11.929</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="X12" t="n">
         <v>0.113</v>
       </c>
-      <c r="K12" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O12" t="n">
-        <v>6.048</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.532</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7.845</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.07099999999999999</v>
-      </c>
       <c r="Y12" t="n">
-        <v>0.123</v>
+        <v>0.172</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.132</v>
+        <v>0.176</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.136</v>
+        <v>0.147</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.132</v>
+        <v>0.129</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.109</v>
+        <v>0.096</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.082</v>
+        <v>0.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.073</v>
+        <v>0.041</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05</v>
+        <v>0.027</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.033</v>
+        <v>0.017</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.022</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="AK12" t="n">
         <v>0.003</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.466</v>
+        <v>0.366</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.396</v>
+        <v>0.294</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.485</v>
+        <v>0.327</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.435</v>
+        <v>0.292</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.5</v>
+        <v>0.325</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.477</v>
+        <v>0.365</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.43</v>
+        <v>0.349</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.433</v>
+        <v>0.341</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.415</v>
+        <v>0.34</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.115</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>823804</v>
+        <v>824126</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2406,150 +2406,150 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHW</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t xml:space="preserve">KC </t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.665</v>
+        <v>4.254</v>
       </c>
       <c r="G13" t="n">
-        <v>0.353</v>
+        <v>0.373</v>
       </c>
       <c r="H13" t="n">
-        <v>0.065</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.187</v>
+        <v>0.174</v>
       </c>
       <c r="J13" t="n">
-        <v>0.12</v>
+        <v>0.107</v>
       </c>
       <c r="K13" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="L13" t="n">
-        <v>1.005</v>
+        <v>1.134</v>
       </c>
       <c r="M13" t="n">
-        <v>0.109</v>
+        <v>0.045</v>
       </c>
       <c r="N13" t="n">
-        <v>1.336</v>
+        <v>1.533</v>
       </c>
       <c r="O13" t="n">
-        <v>4.793</v>
+        <v>4.987</v>
       </c>
       <c r="P13" t="n">
-        <v>2.811</v>
+        <v>3.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.076000000000001</v>
+        <v>7.715</v>
       </c>
       <c r="R13" t="n">
-        <v>0.362</v>
+        <v>0.322</v>
       </c>
       <c r="S13" t="n">
-        <v>0.379</v>
+        <v>0.363</v>
       </c>
       <c r="T13" t="n">
-        <v>0.177</v>
+        <v>0.21</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="V13" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="W13" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AM13" t="n">
         <v>0.004</v>
       </c>
-      <c r="X13" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AN13" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AW13" t="n">
         <v>0.128</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.112</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>823966</v>
+        <v>824293</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2563,150 +2563,150 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.783</v>
+        <v>3.227</v>
       </c>
       <c r="G14" t="n">
-        <v>0.579</v>
+        <v>0.433</v>
       </c>
       <c r="H14" t="n">
-        <v>0.118</v>
+        <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.33</v>
+        <v>0.194</v>
       </c>
       <c r="J14" t="n">
-        <v>0.081</v>
+        <v>0.125</v>
       </c>
       <c r="K14" t="n">
-        <v>0.158</v>
+        <v>0.239</v>
       </c>
       <c r="L14" t="n">
-        <v>1.201</v>
+        <v>0.578</v>
       </c>
       <c r="M14" t="n">
-        <v>0.111</v>
+        <v>0.151</v>
       </c>
       <c r="N14" t="n">
-        <v>1.606</v>
+        <v>1.426</v>
       </c>
       <c r="O14" t="n">
-        <v>4.792</v>
+        <v>5.16</v>
       </c>
       <c r="P14" t="n">
-        <v>4.908</v>
+        <v>2.375</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.997999999999999</v>
+        <v>10.165</v>
       </c>
       <c r="R14" t="n">
-        <v>0.304</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.369</v>
+        <v>0.325</v>
       </c>
       <c r="T14" t="n">
-        <v>0.197</v>
+        <v>0.095</v>
       </c>
       <c r="U14" t="n">
-        <v>0.093</v>
+        <v>0.015</v>
       </c>
       <c r="V14" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.024</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.056</v>
-      </c>
       <c r="AG14" t="n">
-        <v>0.042</v>
+        <v>0.019</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.024</v>
+        <v>0.008</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.585</v>
+        <v>0.321</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.266</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.57</v>
+        <v>0.294</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.526</v>
+        <v>0.305</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.491</v>
+        <v>0.292</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.458</v>
+        <v>0.346</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.457</v>
+        <v>0.348</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.456</v>
+        <v>0.397</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.432</v>
+        <v>0.404</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.135</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>824533</v>
+        <v>824696</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2720,150 +2720,150 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.95</v>
+        <v>5.675</v>
       </c>
       <c r="G15" t="n">
-        <v>0.456</v>
+        <v>0.484</v>
       </c>
       <c r="H15" t="n">
-        <v>0.098</v>
+        <v>0.095</v>
       </c>
       <c r="I15" t="n">
-        <v>0.22</v>
+        <v>0.277</v>
       </c>
       <c r="J15" t="n">
-        <v>0.099</v>
+        <v>0.093</v>
       </c>
       <c r="K15" t="n">
-        <v>0.242</v>
+        <v>0.277</v>
       </c>
       <c r="L15" t="n">
-        <v>1.004</v>
+        <v>1.697</v>
       </c>
       <c r="M15" t="n">
-        <v>0.065</v>
+        <v>0.126</v>
       </c>
       <c r="N15" t="n">
-        <v>1.362</v>
+        <v>2.135</v>
       </c>
       <c r="O15" t="n">
-        <v>4.892</v>
+        <v>5.458</v>
       </c>
       <c r="P15" t="n">
-        <v>3.864</v>
+        <v>3.415</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.474</v>
+        <v>8.523</v>
       </c>
       <c r="R15" t="n">
-        <v>0.372</v>
+        <v>0.194</v>
       </c>
       <c r="S15" t="n">
-        <v>0.36</v>
+        <v>0.301</v>
       </c>
       <c r="T15" t="n">
-        <v>0.187</v>
+        <v>0.257</v>
       </c>
       <c r="U15" t="n">
-        <v>0.059</v>
+        <v>0.148</v>
       </c>
       <c r="V15" t="n">
-        <v>0.015</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>0.006</v>
+        <v>0.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0.074</v>
+        <v>0.028</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.055</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.154</v>
+        <v>0.091</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.153</v>
+        <v>0.122</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.138</v>
+        <v>0.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.106</v>
+        <v>0.111</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.082</v>
+        <v>0.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.068</v>
+        <v>0.103</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.035</v>
+        <v>0.066</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.026</v>
+        <v>0.057</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.017</v>
+        <v>0.049</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.45</v>
+        <v>0.606</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.335</v>
+        <v>0.584</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.383</v>
+        <v>0.591</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.405</v>
+        <v>0.551</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.384</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.421</v>
+        <v>0.631</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.426</v>
+        <v>0.598</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.444</v>
+        <v>0.613</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.436</v>
+        <v>0.661</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.173</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>824859</v>
+        <v>824938</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2877,145 +2877,145 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SF </t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.294</v>
+        <v>3.666</v>
       </c>
       <c r="G16" t="n">
-        <v>0.481</v>
+        <v>0.43</v>
       </c>
       <c r="H16" t="n">
-        <v>0.097</v>
+        <v>0.095</v>
       </c>
       <c r="I16" t="n">
-        <v>0.255</v>
+        <v>0.21</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1</v>
+        <v>0.113</v>
       </c>
       <c r="K16" t="n">
-        <v>0.245</v>
+        <v>0.273</v>
       </c>
       <c r="L16" t="n">
-        <v>0.706</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.129</v>
+        <v>0.066</v>
       </c>
       <c r="N16" t="n">
-        <v>1.542</v>
+        <v>1.59</v>
       </c>
       <c r="O16" t="n">
-        <v>5.904</v>
+        <v>5.101</v>
       </c>
       <c r="P16" t="n">
-        <v>3.96</v>
+        <v>3.084</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.916</v>
+        <v>10.027</v>
       </c>
       <c r="R16" t="n">
-        <v>0.491</v>
+        <v>0.451</v>
       </c>
       <c r="S16" t="n">
         <v>0.352</v>
       </c>
       <c r="T16" t="n">
-        <v>0.126</v>
+        <v>0.142</v>
       </c>
       <c r="U16" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AG16" t="n">
         <v>0.023</v>
       </c>
-      <c r="V16" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.032</v>
-      </c>
       <c r="AH16" t="n">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="AK16" t="n">
         <v>0.003</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.53</v>
+        <v>0.421</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.447</v>
+        <v>0.348</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.495</v>
+        <v>0.405</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.431</v>
+        <v>0.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.468</v>
+        <v>0.39</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.435</v>
+        <v>0.387</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.411</v>
+        <v>0.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.394</v>
+        <v>0.367</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.402</v>
+        <v>0.356</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="17">
@@ -3043,136 +3043,136 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.147</v>
+        <v>3.94</v>
       </c>
       <c r="G17" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="H17" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.096</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.104</v>
-      </c>
       <c r="K17" t="n">
-        <v>0.303</v>
+        <v>0.302</v>
       </c>
       <c r="L17" t="n">
-        <v>1.052</v>
+        <v>0.986</v>
       </c>
       <c r="M17" t="n">
-        <v>0.115</v>
+        <v>0.111</v>
       </c>
       <c r="N17" t="n">
-        <v>1.558</v>
+        <v>1.561</v>
       </c>
       <c r="O17" t="n">
-        <v>4.916</v>
+        <v>4.821</v>
       </c>
       <c r="P17" t="n">
-        <v>3.427</v>
+        <v>3.382</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.071999999999999</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>0.344</v>
+        <v>0.372</v>
       </c>
       <c r="S17" t="n">
-        <v>0.381</v>
+        <v>0.369</v>
       </c>
       <c r="T17" t="n">
         <v>0.183</v>
       </c>
       <c r="U17" t="n">
-        <v>0.067</v>
+        <v>0.056</v>
       </c>
       <c r="V17" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="W17" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="X17" t="n">
-        <v>0.06</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.107</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.15</v>
+        <v>0.152</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.151</v>
+        <v>0.145</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.117</v>
+        <v>0.112</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.03</v>
+        <v>0.024</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AM17" t="n">
         <v>0.002</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.423</v>
+        <v>0.396</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.43</v>
+        <v>0.389</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.443</v>
+        <v>0.431</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.465</v>
+        <v>0.385</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.477</v>
+        <v>0.464</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.483</v>
+        <v>0.435</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.462</v>
+        <v>0.495</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.298</v>
+        <v>0.264</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.112</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="18">
@@ -3514,97 +3514,97 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.711</v>
+        <v>4.673</v>
       </c>
       <c r="G20" t="n">
-        <v>0.647</v>
+        <v>0.628</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12</v>
+        <v>0.129</v>
       </c>
       <c r="I20" t="n">
-        <v>0.339</v>
+        <v>0.326</v>
       </c>
       <c r="J20" t="n">
-        <v>0.065</v>
+        <v>0.076</v>
       </c>
       <c r="K20" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.453</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.324</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="T20" t="n">
         <v>0.187</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.077</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.573</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.744</v>
-      </c>
-      <c r="P20" t="n">
-        <v>4.546</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.202</v>
       </c>
       <c r="U20" t="n">
         <v>0.07199999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="W20" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="X20" t="n">
-        <v>0.049</v>
+        <v>0.047</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.122</v>
+        <v>0.128</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.131</v>
+        <v>0.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.133</v>
+        <v>0.124</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="AK20" t="n">
         <v>0.006</v>
@@ -3613,37 +3613,37 @@
         <v>0.004</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.537</v>
+        <v>0.553</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.532</v>
+        <v>0.484</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.467</v>
+        <v>0.489</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.502</v>
+        <v>0.52</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.528</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.579</v>
+        <v>0.554</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.599</v>
+        <v>0.621</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.238</v>
+        <v>0.239</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.122</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="21">
@@ -3985,70 +3985,70 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.276</v>
+        <v>4.267</v>
       </c>
       <c r="G23" t="n">
-        <v>0.519</v>
+        <v>0.517</v>
       </c>
       <c r="H23" t="n">
         <v>0.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.245</v>
+        <v>0.249</v>
       </c>
       <c r="J23" t="n">
-        <v>0.097</v>
+        <v>0.102</v>
       </c>
       <c r="K23" t="n">
-        <v>0.255</v>
+        <v>0.261</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="M23" t="n">
-        <v>0.082</v>
+        <v>0.09</v>
       </c>
       <c r="N23" t="n">
-        <v>1.606</v>
+        <v>1.612</v>
       </c>
       <c r="O23" t="n">
-        <v>5.261</v>
+        <v>5.32</v>
       </c>
       <c r="P23" t="n">
-        <v>4.466</v>
+        <v>4.395</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.867</v>
+        <v>7.787</v>
       </c>
       <c r="R23" t="n">
-        <v>0.503</v>
+        <v>0.52</v>
       </c>
       <c r="S23" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="T23" t="n">
-        <v>0.123</v>
+        <v>0.121</v>
       </c>
       <c r="U23" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="V23" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="W23" t="n">
         <v>0.001</v>
       </c>
       <c r="X23" t="n">
-        <v>0.068</v>
+        <v>0.058</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.129</v>
+        <v>0.147</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.146</v>
+        <v>0.149</v>
       </c>
       <c r="AB23" t="n">
         <v>0.132</v>
@@ -4057,64 +4057,64 @@
         <v>0.111</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.096</v>
+        <v>0.083</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="AH23" t="n">
         <v>0.022</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="AK23" t="n">
         <v>0.006</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AM23" t="n">
         <v>0.003</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.523</v>
+        <v>0.503</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.456</v>
+        <v>0.446</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.445</v>
+        <v>0.459</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.461</v>
+        <v>0.455</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.461</v>
+        <v>0.481</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.521</v>
+        <v>0.481</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.492</v>
+        <v>0.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.257</v>
+        <v>0.248</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.12</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="24">

--- a/data/live/BallparkPal_Teams_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Teams_2026-04-12.xlsx
@@ -665,7 +665,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>822828</v>
+        <v>822998</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -679,150 +679,150 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t xml:space="preserve">TB </t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.593</v>
+        <v>4.505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.54</v>
+        <v>0.582</v>
       </c>
       <c r="H2" t="n">
-        <v>0.096</v>
+        <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>0.302</v>
+        <v>0.319</v>
       </c>
       <c r="J2" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.501</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.503</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.662</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9.246</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.097</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.483</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.664</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4.777</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.362</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>9.083</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.09</v>
-      </c>
       <c r="Z2" t="n">
-        <v>0.131</v>
+        <v>0.13</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.133</v>
+        <v>0.138</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.127</v>
+        <v>0.145</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.138</v>
+        <v>0.119</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.111</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.074</v>
+        <v>0.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AM2" t="n">
         <v>0.004</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.579</v>
+        <v>0.504</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.539</v>
+        <v>0.385</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.578</v>
+        <v>0.456</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.553</v>
+        <v>0.457</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.538</v>
+        <v>0.431</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.431</v>
+        <v>0.501</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.404</v>
+        <v>0.489</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.398</v>
+        <v>0.513</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.348</v>
+        <v>0.514</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.133</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>823154</v>
+        <v>823075</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -836,150 +836,150 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.941</v>
+        <v>4.705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.426</v>
+        <v>0.533</v>
       </c>
       <c r="H3" t="n">
-        <v>0.089</v>
+        <v>0.113</v>
       </c>
       <c r="I3" t="n">
-        <v>0.21</v>
+        <v>0.294</v>
       </c>
       <c r="J3" t="n">
-        <v>0.11</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.279</v>
+        <v>0.233</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>0.857</v>
       </c>
       <c r="M3" t="n">
-        <v>0.075</v>
+        <v>0.161</v>
       </c>
       <c r="N3" t="n">
-        <v>1.426</v>
+        <v>1.787</v>
       </c>
       <c r="O3" t="n">
-        <v>5.015</v>
+        <v>5.603</v>
       </c>
       <c r="P3" t="n">
-        <v>2.576</v>
+        <v>4.126</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.553000000000001</v>
+        <v>7.029</v>
       </c>
       <c r="R3" t="n">
-        <v>0.289</v>
+        <v>0.427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.363</v>
+        <v>0.357</v>
       </c>
       <c r="T3" t="n">
-        <v>0.22</v>
+        <v>0.161</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09</v>
+        <v>0.044</v>
       </c>
       <c r="V3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0.027</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.015</v>
-      </c>
       <c r="AI3" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="AL3" t="n">
         <v>0.002</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.431</v>
+        <v>0.543</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.386</v>
+        <v>0.491</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.392</v>
+        <v>0.535</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.391</v>
+        <v>0.543</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.385</v>
+        <v>0.478</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.419</v>
+        <v>0.491</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.434</v>
+        <v>0.457</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.419</v>
+        <v>0.438</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.45</v>
+        <v>0.441</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.156</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>823479</v>
+        <v>823317</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -993,150 +993,150 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t xml:space="preserve">SD </t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.257</v>
+        <v>3.012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.436</v>
+        <v>0.327</v>
       </c>
       <c r="H4" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25</v>
+        <v>0.132</v>
       </c>
       <c r="J4" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.239</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.804</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>10.823</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.113</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O4" t="n">
-        <v>6.048</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.532</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7.845</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.132</v>
-      </c>
       <c r="AC4" t="n">
-        <v>0.109</v>
+        <v>0.092</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.082</v>
+        <v>0.063</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.073</v>
+        <v>0.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.05</v>
+        <v>0.021</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.033</v>
+        <v>0.014</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.466</v>
+        <v>0.314</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.396</v>
+        <v>0.281</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.485</v>
+        <v>0.314</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.435</v>
+        <v>0.29</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.5</v>
+        <v>0.297</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.477</v>
+        <v>0.31</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.43</v>
+        <v>0.327</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.433</v>
+        <v>0.348</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.415</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>823804</v>
+        <v>823642</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1150,150 +1150,150 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.667</v>
+        <v>3.23</v>
       </c>
       <c r="G5" t="n">
-        <v>0.372</v>
+        <v>0.426</v>
       </c>
       <c r="H5" t="n">
-        <v>0.076</v>
+        <v>0.107</v>
       </c>
       <c r="I5" t="n">
-        <v>0.179</v>
+        <v>0.184</v>
       </c>
       <c r="J5" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.378</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.002</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>11.929</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.129</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.318</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.784</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.879</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>9.087</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.127</v>
-      </c>
       <c r="AC5" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.054</v>
+        <v>0.041</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.041</v>
+        <v>0.027</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.014</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AI5" t="n">
         <v>0.006</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AK5" t="n">
         <v>0.003</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.399</v>
+        <v>0.366</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.362</v>
+        <v>0.294</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.382</v>
+        <v>0.327</v>
       </c>
       <c r="AQ5" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AS5" t="n">
         <v>0.365</v>
       </c>
-      <c r="AR5" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AT5" t="n">
-        <v>0.359</v>
+        <v>0.349</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.438</v>
+        <v>0.341</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.389</v>
+        <v>0.34</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.134</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>823966</v>
+        <v>824126</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1307,150 +1307,150 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHW</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t xml:space="preserve">KC </t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.783</v>
+        <v>4.254</v>
       </c>
       <c r="G6" t="n">
-        <v>0.579</v>
+        <v>0.373</v>
       </c>
       <c r="H6" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.987</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.715</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.118</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.201</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.606</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.792</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4.908</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8.997999999999999</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.114</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0.092</v>
+        <v>0.099</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.056</v>
+        <v>0.049</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.042</v>
+        <v>0.033</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.585</v>
+        <v>0.513</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.526</v>
+        <v>0.437</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.491</v>
+        <v>0.457</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.458</v>
+        <v>0.433</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.457</v>
+        <v>0.432</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.456</v>
+        <v>0.428</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.432</v>
+        <v>0.391</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.135</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>824533</v>
+        <v>824293</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1464,150 +1464,150 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>3.227</v>
       </c>
       <c r="G7" t="n">
-        <v>0.456</v>
+        <v>0.433</v>
       </c>
       <c r="H7" t="n">
-        <v>0.098</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.22</v>
+        <v>0.194</v>
       </c>
       <c r="J7" t="n">
-        <v>0.099</v>
+        <v>0.125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.242</v>
+        <v>0.239</v>
       </c>
       <c r="L7" t="n">
-        <v>1.004</v>
+        <v>0.578</v>
       </c>
       <c r="M7" t="n">
-        <v>0.065</v>
+        <v>0.151</v>
       </c>
       <c r="N7" t="n">
-        <v>1.362</v>
+        <v>1.426</v>
       </c>
       <c r="O7" t="n">
-        <v>4.892</v>
+        <v>5.16</v>
       </c>
       <c r="P7" t="n">
-        <v>3.864</v>
+        <v>2.375</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.474</v>
+        <v>10.165</v>
       </c>
       <c r="R7" t="n">
-        <v>0.372</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.36</v>
+        <v>0.325</v>
       </c>
       <c r="T7" t="n">
-        <v>0.187</v>
+        <v>0.095</v>
       </c>
       <c r="U7" t="n">
-        <v>0.059</v>
+        <v>0.015</v>
       </c>
       <c r="V7" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.006</v>
       </c>
-      <c r="X7" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.012</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.45</v>
+        <v>0.321</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.335</v>
+        <v>0.266</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.383</v>
+        <v>0.294</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.405</v>
+        <v>0.305</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.384</v>
+        <v>0.292</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.421</v>
+        <v>0.346</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.426</v>
+        <v>0.348</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.444</v>
+        <v>0.397</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.436</v>
+        <v>0.404</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.173</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>824859</v>
+        <v>824696</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1621,150 +1621,150 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SF </t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.255</v>
+        <v>5.675</v>
       </c>
       <c r="G8" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="H8" t="n">
-        <v>0.102</v>
+        <v>0.095</v>
       </c>
       <c r="I8" t="n">
-        <v>0.261</v>
+        <v>0.277</v>
       </c>
       <c r="J8" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.697</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.458</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8.523</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AD8" t="n">
         <v>0.1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.599</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5.655</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.879</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8.887</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AE8" t="n">
         <v>0.103</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.067</v>
-      </c>
       <c r="AF8" t="n">
-        <v>0.051</v>
+        <v>0.066</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.034</v>
+        <v>0.057</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.022</v>
+        <v>0.049</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.015</v>
+        <v>0.029</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AL8" t="n">
         <v>0.005</v>
       </c>
-      <c r="AK8" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.002</v>
-      </c>
       <c r="AM8" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.533</v>
+        <v>0.606</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.445</v>
+        <v>0.584</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.495</v>
+        <v>0.591</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.484</v>
+        <v>0.551</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.446</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.399</v>
+        <v>0.631</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.395</v>
+        <v>0.598</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.399</v>
+        <v>0.613</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.385</v>
+        <v>0.661</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.149</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>822998</v>
+        <v>824938</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1778,150 +1778,150 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB </t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.505</v>
+        <v>3.666</v>
       </c>
       <c r="G9" t="n">
-        <v>0.582</v>
+        <v>0.43</v>
       </c>
       <c r="H9" t="n">
-        <v>0.122</v>
+        <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.319</v>
+        <v>0.21</v>
       </c>
       <c r="J9" t="n">
-        <v>0.082</v>
+        <v>0.113</v>
       </c>
       <c r="K9" t="n">
-        <v>0.163</v>
+        <v>0.273</v>
       </c>
       <c r="L9" t="n">
-        <v>1.385</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.12</v>
+        <v>0.066</v>
       </c>
       <c r="N9" t="n">
-        <v>1.501</v>
+        <v>1.59</v>
       </c>
       <c r="O9" t="n">
-        <v>4.503</v>
+        <v>5.101</v>
       </c>
       <c r="P9" t="n">
-        <v>3.662</v>
+        <v>3.084</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.246</v>
+        <v>10.027</v>
       </c>
       <c r="R9" t="n">
-        <v>0.272</v>
+        <v>0.451</v>
       </c>
       <c r="S9" t="n">
-        <v>0.33</v>
+        <v>0.352</v>
       </c>
       <c r="T9" t="n">
-        <v>0.222</v>
+        <v>0.142</v>
       </c>
       <c r="U9" t="n">
-        <v>0.117</v>
+        <v>0.043</v>
       </c>
       <c r="V9" t="n">
-        <v>0.043</v>
+        <v>0.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05</v>
+        <v>0.093</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.097</v>
+        <v>0.141</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.13</v>
+        <v>0.148</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.138</v>
+        <v>0.157</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.145</v>
+        <v>0.134</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.119</v>
+        <v>0.111</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.08</v>
+        <v>0.048</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.058</v>
+        <v>0.032</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.035</v>
+        <v>0.023</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.015</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.504</v>
+        <v>0.421</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.385</v>
+        <v>0.348</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.456</v>
+        <v>0.405</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.457</v>
+        <v>0.36</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.431</v>
+        <v>0.39</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.501</v>
+        <v>0.387</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.489</v>
+        <v>0.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.513</v>
+        <v>0.367</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.514</v>
+        <v>0.356</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.158</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>823075</v>
+        <v>822828</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1935,150 +1935,150 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.705</v>
+        <v>4.593</v>
       </c>
       <c r="G10" t="n">
-        <v>0.533</v>
+        <v>0.54</v>
       </c>
       <c r="H10" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.362</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9.083</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="U10" t="n">
         <v>0.113</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.787</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5.603</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.126</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.029</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.044</v>
-      </c>
       <c r="V10" t="n">
-        <v>0.008</v>
+        <v>0.048</v>
       </c>
       <c r="W10" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="X10" t="n">
-        <v>0.049</v>
+        <v>0.043</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.093</v>
+        <v>0.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.115</v>
+        <v>0.131</v>
       </c>
       <c r="AA10" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AC10" t="n">
         <v>0.138</v>
       </c>
-      <c r="AB10" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.114</v>
-      </c>
       <c r="AD10" t="n">
-        <v>0.104</v>
+        <v>0.111</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.081</v>
+        <v>0.074</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.042</v>
+        <v>0.039</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AL10" t="n">
         <v>0.002</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.543</v>
+        <v>0.579</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.491</v>
+        <v>0.539</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.535</v>
+        <v>0.578</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.543</v>
+        <v>0.553</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.478</v>
+        <v>0.538</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.491</v>
+        <v>0.431</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.457</v>
+        <v>0.404</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.438</v>
+        <v>0.398</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.441</v>
+        <v>0.348</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.149</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>823317</v>
+        <v>823154</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2092,150 +2092,150 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD </t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.892</v>
+        <v>3.941</v>
       </c>
       <c r="G11" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.015</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.553000000000001</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.289</v>
       </c>
-      <c r="H11" t="n">
+      <c r="S11" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.951</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.938</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.857</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>11.654</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AK11" t="n">
         <v>0.004</v>
       </c>
-      <c r="X11" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM11" t="n">
         <v>0.001</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.318</v>
+        <v>0.431</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.256</v>
+        <v>0.386</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.287</v>
+        <v>0.392</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.258</v>
+        <v>0.391</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.302</v>
+        <v>0.385</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.312</v>
+        <v>0.419</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.332</v>
+        <v>0.434</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.334</v>
+        <v>0.419</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.09</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>823642</v>
+        <v>823479</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2249,150 +2249,150 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.23</v>
+        <v>4.257</v>
       </c>
       <c r="G12" t="n">
-        <v>0.426</v>
+        <v>0.436</v>
       </c>
       <c r="H12" t="n">
-        <v>0.107</v>
+        <v>0.079</v>
       </c>
       <c r="I12" t="n">
-        <v>0.184</v>
+        <v>0.25</v>
       </c>
       <c r="J12" t="n">
-        <v>0.121</v>
+        <v>0.113</v>
       </c>
       <c r="K12" t="n">
-        <v>0.245</v>
+        <v>0.267</v>
       </c>
       <c r="L12" t="n">
-        <v>0.716</v>
+        <v>0.822</v>
       </c>
       <c r="M12" t="n">
-        <v>0.097</v>
+        <v>0.152</v>
       </c>
       <c r="N12" t="n">
-        <v>1.316</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>4.378</v>
+        <v>6.048</v>
       </c>
       <c r="P12" t="n">
-        <v>4.002</v>
+        <v>3.532</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.929</v>
+        <v>7.845</v>
       </c>
       <c r="R12" t="n">
-        <v>0.504</v>
+        <v>0.449</v>
       </c>
       <c r="S12" t="n">
-        <v>0.325</v>
+        <v>0.349</v>
       </c>
       <c r="T12" t="n">
-        <v>0.131</v>
+        <v>0.146</v>
       </c>
       <c r="U12" t="n">
-        <v>0.032</v>
+        <v>0.045</v>
       </c>
       <c r="V12" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="W12" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="X12" t="n">
-        <v>0.113</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.172</v>
+        <v>0.123</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.176</v>
+        <v>0.132</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.147</v>
+        <v>0.136</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.096</v>
+        <v>0.109</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.06</v>
+        <v>0.082</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.041</v>
+        <v>0.073</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.027</v>
+        <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.017</v>
+        <v>0.033</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="AK12" t="n">
         <v>0.003</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.366</v>
+        <v>0.466</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.294</v>
+        <v>0.396</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.327</v>
+        <v>0.485</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.292</v>
+        <v>0.435</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.325</v>
+        <v>0.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.365</v>
+        <v>0.477</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.349</v>
+        <v>0.43</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.341</v>
+        <v>0.433</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.34</v>
+        <v>0.415</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.145</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>824126</v>
+        <v>823804</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2406,150 +2406,150 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC </t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.254</v>
+        <v>3.667</v>
       </c>
       <c r="G13" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I13" t="n">
-        <v>0.174</v>
+        <v>0.179</v>
       </c>
       <c r="J13" t="n">
-        <v>0.107</v>
+        <v>0.129</v>
       </c>
       <c r="K13" t="n">
-        <v>0.338</v>
+        <v>0.326</v>
       </c>
       <c r="L13" t="n">
-        <v>1.134</v>
+        <v>1.012</v>
       </c>
       <c r="M13" t="n">
-        <v>0.045</v>
+        <v>0.098</v>
       </c>
       <c r="N13" t="n">
-        <v>1.533</v>
+        <v>1.318</v>
       </c>
       <c r="O13" t="n">
-        <v>4.987</v>
+        <v>4.784</v>
       </c>
       <c r="P13" t="n">
-        <v>3.38</v>
+        <v>2.879</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.715</v>
+        <v>9.087</v>
       </c>
       <c r="R13" t="n">
-        <v>0.322</v>
+        <v>0.37</v>
       </c>
       <c r="S13" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="T13" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="V13" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="X13" t="n">
-        <v>0.062</v>
+        <v>0.097</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.106</v>
+        <v>0.138</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.133</v>
+        <v>0.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.149</v>
+        <v>0.163</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.137</v>
+        <v>0.127</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.118</v>
+        <v>0.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.099</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.049</v>
+        <v>0.041</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AK13" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AL13" t="n">
         <v>0.002</v>
       </c>
-      <c r="AL13" t="n">
-        <v>0.003</v>
-      </c>
       <c r="AM13" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.513</v>
+        <v>0.399</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.442</v>
+        <v>0.362</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5</v>
+        <v>0.382</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.437</v>
+        <v>0.365</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.457</v>
+        <v>0.355</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.433</v>
+        <v>0.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.432</v>
+        <v>0.359</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.428</v>
+        <v>0.438</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.128</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>824293</v>
+        <v>823966</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2563,150 +2563,150 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.227</v>
+        <v>4.596</v>
       </c>
       <c r="G14" t="n">
-        <v>0.433</v>
+        <v>0.59</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.116</v>
       </c>
       <c r="I14" t="n">
-        <v>0.194</v>
+        <v>0.338</v>
       </c>
       <c r="J14" t="n">
-        <v>0.125</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.239</v>
+        <v>0.136</v>
       </c>
       <c r="L14" t="n">
-        <v>0.578</v>
+        <v>1.146</v>
       </c>
       <c r="M14" t="n">
-        <v>0.151</v>
+        <v>0.111</v>
       </c>
       <c r="N14" t="n">
-        <v>1.426</v>
+        <v>1.641</v>
       </c>
       <c r="O14" t="n">
-        <v>5.16</v>
+        <v>4.827</v>
       </c>
       <c r="P14" t="n">
-        <v>2.375</v>
+        <v>4.593</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.165</v>
+        <v>9.003</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.326</v>
       </c>
       <c r="S14" t="n">
-        <v>0.325</v>
+        <v>0.361</v>
       </c>
       <c r="T14" t="n">
-        <v>0.095</v>
+        <v>0.199</v>
       </c>
       <c r="U14" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AI14" t="n">
         <v>0.015</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AJ14" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AL14" t="n">
         <v>0.004</v>
       </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AI14" t="n">
+      <c r="AM14" t="n">
         <v>0.006</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AN14" t="n">
-        <v>0.321</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.266</v>
+        <v>0.507</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.294</v>
+        <v>0.593</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.305</v>
+        <v>0.507</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.292</v>
+        <v>0.499</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.346</v>
+        <v>0.435</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.348</v>
+        <v>0.395</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.397</v>
+        <v>0.43</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.404</v>
+        <v>0.409</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.159</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>824696</v>
+        <v>824533</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2720,150 +2720,150 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.675</v>
+        <v>3.95</v>
       </c>
       <c r="G15" t="n">
-        <v>0.484</v>
+        <v>0.456</v>
       </c>
       <c r="H15" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="I15" t="n">
-        <v>0.277</v>
+        <v>0.22</v>
       </c>
       <c r="J15" t="n">
-        <v>0.093</v>
+        <v>0.099</v>
       </c>
       <c r="K15" t="n">
-        <v>0.277</v>
+        <v>0.242</v>
       </c>
       <c r="L15" t="n">
-        <v>1.697</v>
+        <v>1.004</v>
       </c>
       <c r="M15" t="n">
-        <v>0.126</v>
+        <v>0.065</v>
       </c>
       <c r="N15" t="n">
-        <v>2.135</v>
+        <v>1.362</v>
       </c>
       <c r="O15" t="n">
-        <v>5.458</v>
+        <v>4.892</v>
       </c>
       <c r="P15" t="n">
-        <v>3.415</v>
+        <v>3.864</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.523</v>
+        <v>9.474</v>
       </c>
       <c r="R15" t="n">
-        <v>0.194</v>
+        <v>0.372</v>
       </c>
       <c r="S15" t="n">
-        <v>0.301</v>
+        <v>0.36</v>
       </c>
       <c r="T15" t="n">
-        <v>0.257</v>
+        <v>0.187</v>
       </c>
       <c r="U15" t="n">
-        <v>0.148</v>
+        <v>0.059</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.015</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03</v>
+        <v>0.006</v>
       </c>
       <c r="X15" t="n">
-        <v>0.028</v>
+        <v>0.074</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.055</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.091</v>
+        <v>0.154</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.122</v>
+        <v>0.153</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.13</v>
+        <v>0.138</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.111</v>
+        <v>0.106</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1</v>
+        <v>0.082</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.103</v>
+        <v>0.068</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.066</v>
+        <v>0.035</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.057</v>
+        <v>0.026</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.049</v>
+        <v>0.017</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.606</v>
+        <v>0.45</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.584</v>
+        <v>0.335</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.591</v>
+        <v>0.383</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.551</v>
+        <v>0.405</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.384</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.631</v>
+        <v>0.421</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.598</v>
+        <v>0.426</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.613</v>
+        <v>0.444</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.661</v>
+        <v>0.436</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.17</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>824938</v>
+        <v>824859</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2877,106 +2877,106 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t xml:space="preserve">SF </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.666</v>
+        <v>4.255</v>
       </c>
       <c r="G16" t="n">
-        <v>0.43</v>
+        <v>0.483</v>
       </c>
       <c r="H16" t="n">
-        <v>0.095</v>
+        <v>0.102</v>
       </c>
       <c r="I16" t="n">
-        <v>0.21</v>
+        <v>0.261</v>
       </c>
       <c r="J16" t="n">
-        <v>0.113</v>
+        <v>0.1</v>
       </c>
       <c r="K16" t="n">
-        <v>0.273</v>
+        <v>0.249</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="M16" t="n">
-        <v>0.066</v>
+        <v>0.091</v>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>1.599</v>
       </c>
       <c r="O16" t="n">
-        <v>5.101</v>
+        <v>5.655</v>
       </c>
       <c r="P16" t="n">
-        <v>3.084</v>
+        <v>3.879</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.027</v>
+        <v>8.887</v>
       </c>
       <c r="R16" t="n">
-        <v>0.451</v>
+        <v>0.44</v>
       </c>
       <c r="S16" t="n">
-        <v>0.352</v>
+        <v>0.363</v>
       </c>
       <c r="T16" t="n">
-        <v>0.142</v>
+        <v>0.145</v>
       </c>
       <c r="U16" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="W16" t="n">
         <v>0.002</v>
       </c>
       <c r="X16" t="n">
-        <v>0.093</v>
+        <v>0.062</v>
       </c>
       <c r="Y16" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AA16" t="n">
         <v>0.141</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.157</v>
-      </c>
       <c r="AB16" t="n">
-        <v>0.134</v>
+        <v>0.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.111</v>
+        <v>0.119</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.048</v>
+        <v>0.067</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.032</v>
+        <v>0.051</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.023</v>
+        <v>0.034</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="AK16" t="n">
         <v>0.003</v>
@@ -2988,39 +2988,39 @@
         <v>0.003</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.421</v>
+        <v>0.533</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.348</v>
+        <v>0.445</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.405</v>
+        <v>0.495</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.36</v>
+        <v>0.484</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.39</v>
+        <v>0.446</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.387</v>
+        <v>0.399</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.367</v>
+        <v>0.399</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.356</v>
+        <v>0.385</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.142</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>822828</v>
+        <v>822998</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3034,106 +3034,106 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t xml:space="preserve">TB </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.94</v>
+        <v>3.546</v>
       </c>
       <c r="G17" t="n">
-        <v>0.46</v>
+        <v>0.418</v>
       </c>
       <c r="H17" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="M17" t="n">
         <v>0.097</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.986</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.111</v>
-      </c>
       <c r="N17" t="n">
-        <v>1.561</v>
+        <v>1.586</v>
       </c>
       <c r="O17" t="n">
-        <v>4.821</v>
+        <v>4.747</v>
       </c>
       <c r="P17" t="n">
-        <v>3.382</v>
+        <v>3.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.217000000000001</v>
+        <v>8.853999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>0.372</v>
+        <v>0.518</v>
       </c>
       <c r="S17" t="n">
-        <v>0.369</v>
+        <v>0.333</v>
       </c>
       <c r="T17" t="n">
-        <v>0.183</v>
+        <v>0.118</v>
       </c>
       <c r="U17" t="n">
-        <v>0.056</v>
+        <v>0.026</v>
       </c>
       <c r="V17" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="W17" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="X17" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.097</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0.142</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.148</v>
+        <v>0.167</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.145</v>
+        <v>0.132</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.112</v>
+        <v>0.101</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.093</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.057</v>
+        <v>0.048</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.042</v>
+        <v>0.027</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="AI17" t="n">
         <v>0.008</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AK17" t="n">
         <v>0.002</v>
@@ -3142,42 +3142,42 @@
         <v>0.002</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.458</v>
+        <v>0.379</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.396</v>
+        <v>0.332</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.389</v>
+        <v>0.316</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.431</v>
+        <v>0.339</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.385</v>
+        <v>0.347</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.464</v>
+        <v>0.374</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.435</v>
+        <v>0.438</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.495</v>
+        <v>0.538</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.264</v>
+        <v>0.29</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.122</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>823154</v>
+        <v>823075</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3191,100 +3191,100 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.426</v>
+        <v>4.383</v>
       </c>
       <c r="G18" t="n">
-        <v>0.574</v>
+        <v>0.467</v>
       </c>
       <c r="H18" t="n">
-        <v>0.11</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.279</v>
+        <v>0.233</v>
       </c>
       <c r="J18" t="n">
-        <v>0.089</v>
+        <v>0.113</v>
       </c>
       <c r="K18" t="n">
-        <v>0.21</v>
+        <v>0.294</v>
       </c>
       <c r="L18" t="n">
-        <v>1.112</v>
+        <v>0.879</v>
       </c>
       <c r="M18" t="n">
-        <v>0.079</v>
+        <v>0.059</v>
       </c>
       <c r="N18" t="n">
-        <v>1.356</v>
+        <v>1.76</v>
       </c>
       <c r="O18" t="n">
-        <v>4.782</v>
+        <v>5.018</v>
       </c>
       <c r="P18" t="n">
-        <v>4.649</v>
+        <v>4.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.77</v>
+        <v>7.104</v>
       </c>
       <c r="R18" t="n">
-        <v>0.324</v>
+        <v>0.432</v>
       </c>
       <c r="S18" t="n">
-        <v>0.372</v>
+        <v>0.348</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0.065</v>
+        <v>0.053</v>
       </c>
       <c r="V18" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="W18" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="X18" t="n">
-        <v>0.048</v>
+        <v>0.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.105</v>
+        <v>0.094</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.128</v>
+        <v>0.138</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.138</v>
+        <v>0.144</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.103</v>
+        <v>0.09</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AF18" t="n">
         <v>0.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="AI18" t="n">
         <v>0.015</v>
@@ -3296,45 +3296,45 @@
         <v>0.006</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.515</v>
+        <v>0.591</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.48</v>
+        <v>0.487</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.511</v>
+        <v>0.516</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.477</v>
+        <v>0.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.471</v>
+        <v>0.516</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.491</v>
+        <v>0.493</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.508</v>
+        <v>0.407</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.513</v>
+        <v>0.424</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.238</v>
+        <v>0.211</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.124</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>823479</v>
+        <v>823317</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3348,150 +3348,150 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t xml:space="preserve">SD </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.543</v>
+        <v>4.391</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="H19" t="n">
-        <v>0.113</v>
+        <v>0.123</v>
       </c>
       <c r="I19" t="n">
-        <v>0.267</v>
+        <v>0.349</v>
       </c>
       <c r="J19" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.636</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.891</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.207</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="U19" t="n">
         <v>0.079</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.066</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>5.319</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.988</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7.232</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.075</v>
-      </c>
       <c r="V19" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="W19" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="X19" t="n">
-        <v>0.046</v>
+        <v>0.052</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.095</v>
+        <v>0.096</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.134</v>
+        <v>0.126</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.139</v>
+        <v>0.151</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.114</v>
+        <v>0.132</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.103</v>
+        <v>0.089</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.051</v>
+        <v>0.045</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.518</v>
+        <v>0.517</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.443</v>
+        <v>0.462</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.505</v>
+        <v>0.512</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.506</v>
+        <v>0.488</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.502</v>
+        <v>0.479</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.49</v>
+        <v>0.457</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.55</v>
+        <v>0.508</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.239</v>
+        <v>0.182</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>823804</v>
+        <v>823642</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3505,150 +3505,150 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.673</v>
+        <v>3.59</v>
       </c>
       <c r="G20" t="n">
-        <v>0.628</v>
+        <v>0.574</v>
       </c>
       <c r="H20" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="I20" t="n">
-        <v>0.326</v>
+        <v>0.245</v>
       </c>
       <c r="J20" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.662</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.741</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AD20" t="n">
         <v>0.076</v>
       </c>
-      <c r="K20" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.571</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>4.453</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7.324</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.1</v>
-      </c>
       <c r="AE20" t="n">
-        <v>0.08</v>
+        <v>0.053</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.061</v>
+        <v>0.027</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.553</v>
+        <v>0.388</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.46</v>
+        <v>0.397</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.484</v>
+        <v>0.385</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.489</v>
+        <v>0.377</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.52</v>
+        <v>0.384</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.528</v>
+        <v>0.42</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.554</v>
+        <v>0.405</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.621</v>
+        <v>0.416</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.239</v>
+        <v>0.203</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.115</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>823966</v>
+        <v>824126</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3662,150 +3662,150 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t xml:space="preserve">KC </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHW</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.687</v>
+        <v>5.326</v>
       </c>
       <c r="G21" t="n">
-        <v>0.421</v>
+        <v>0.627</v>
       </c>
       <c r="H21" t="n">
-        <v>0.081</v>
+        <v>0.107</v>
       </c>
       <c r="I21" t="n">
-        <v>0.158</v>
+        <v>0.338</v>
       </c>
       <c r="J21" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.979</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.047</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="AW21" t="n">
         <v>0.118</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.912</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3.398</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>10.504</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>824533</v>
+        <v>824293</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3819,150 +3819,150 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.212</v>
+        <v>3.586</v>
       </c>
       <c r="G22" t="n">
-        <v>0.544</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.099</v>
+        <v>0.125</v>
       </c>
       <c r="I22" t="n">
-        <v>0.242</v>
+        <v>0.239</v>
       </c>
       <c r="J22" t="n">
-        <v>0.098</v>
+        <v>0.1</v>
       </c>
       <c r="K22" t="n">
-        <v>0.22</v>
+        <v>0.194</v>
       </c>
       <c r="L22" t="n">
-        <v>0.86</v>
+        <v>0.666</v>
       </c>
       <c r="M22" t="n">
-        <v>0.126</v>
+        <v>0.138</v>
       </c>
       <c r="N22" t="n">
-        <v>1.302</v>
+        <v>1.399</v>
       </c>
       <c r="O22" t="n">
-        <v>4.875</v>
+        <v>4.911</v>
       </c>
       <c r="P22" t="n">
-        <v>4.863</v>
+        <v>3.278</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.882999999999999</v>
+        <v>6.57</v>
       </c>
       <c r="R22" t="n">
-        <v>0.423</v>
+        <v>0.513</v>
       </c>
       <c r="S22" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AO22" t="n">
         <v>0.367</v>
       </c>
-      <c r="T22" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0.441</v>
-      </c>
       <c r="AP22" t="n">
-        <v>0.399</v>
+        <v>0.377</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.443</v>
+        <v>0.353</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.451</v>
+        <v>0.378</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.486</v>
+        <v>0.413</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.533</v>
+        <v>0.403</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.487</v>
+        <v>0.466</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.268</v>
+        <v>0.217</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.138</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>824859</v>
+        <v>824696</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3976,150 +3976,150 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SF </t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.267</v>
+        <v>5.776</v>
       </c>
       <c r="G23" t="n">
-        <v>0.517</v>
+        <v>0.516</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1</v>
+        <v>0.093</v>
       </c>
       <c r="I23" t="n">
-        <v>0.249</v>
+        <v>0.277</v>
       </c>
       <c r="J23" t="n">
-        <v>0.102</v>
+        <v>0.095</v>
       </c>
       <c r="K23" t="n">
-        <v>0.261</v>
+        <v>0.277</v>
       </c>
       <c r="L23" t="n">
-        <v>0.68</v>
+        <v>1.453</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09</v>
+        <v>0.129</v>
       </c>
       <c r="N23" t="n">
-        <v>1.612</v>
+        <v>1.695</v>
       </c>
       <c r="O23" t="n">
-        <v>5.32</v>
+        <v>5.325</v>
       </c>
       <c r="P23" t="n">
-        <v>4.395</v>
+        <v>5.369</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.787</v>
+        <v>9.782</v>
       </c>
       <c r="R23" t="n">
-        <v>0.52</v>
+        <v>0.229</v>
       </c>
       <c r="S23" t="n">
-        <v>0.324</v>
+        <v>0.346</v>
       </c>
       <c r="T23" t="n">
-        <v>0.121</v>
+        <v>0.244</v>
       </c>
       <c r="U23" t="n">
-        <v>0.027</v>
+        <v>0.124</v>
       </c>
       <c r="V23" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
       <c r="W23" t="n">
-        <v>0.001</v>
+        <v>0.017</v>
       </c>
       <c r="X23" t="n">
-        <v>0.058</v>
+        <v>0.026</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.108</v>
+        <v>0.062</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.147</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.149</v>
+        <v>0.101</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.132</v>
+        <v>0.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.083</v>
+        <v>0.117</v>
       </c>
       <c r="AE23" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0.076</v>
       </c>
-      <c r="AF23" t="n">
-        <v>0.05</v>
-      </c>
       <c r="AG23" t="n">
-        <v>0.033</v>
+        <v>0.063</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.022</v>
+        <v>0.043</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.011</v>
+        <v>0.028</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.503</v>
+        <v>0.592</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.44</v>
+        <v>0.587</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.446</v>
+        <v>0.608</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.459</v>
+        <v>0.599</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.455</v>
+        <v>0.64</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.481</v>
+        <v>0.704</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.481</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.5</v>
+        <v>0.742</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.248</v>
+        <v>0.375</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.126</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>822998</v>
+        <v>824938</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4133,150 +4133,150 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TB </t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.546</v>
+        <v>4.101</v>
       </c>
       <c r="G24" t="n">
-        <v>0.418</v>
+        <v>0.57</v>
       </c>
       <c r="H24" t="n">
-        <v>0.082</v>
+        <v>0.113</v>
       </c>
       <c r="I24" t="n">
-        <v>0.163</v>
+        <v>0.273</v>
       </c>
       <c r="J24" t="n">
-        <v>0.122</v>
+        <v>0.095</v>
       </c>
       <c r="K24" t="n">
-        <v>0.319</v>
+        <v>0.21</v>
       </c>
       <c r="L24" t="n">
-        <v>0.671</v>
+        <v>0.91</v>
       </c>
       <c r="M24" t="n">
-        <v>0.097</v>
+        <v>0.127</v>
       </c>
       <c r="N24" t="n">
-        <v>1.586</v>
+        <v>1.688</v>
       </c>
       <c r="O24" t="n">
-        <v>4.747</v>
+        <v>4.819</v>
       </c>
       <c r="P24" t="n">
-        <v>3.232</v>
+        <v>3.449</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.853999999999999</v>
+        <v>7.812</v>
       </c>
       <c r="R24" t="n">
-        <v>0.518</v>
+        <v>0.405</v>
       </c>
       <c r="S24" t="n">
-        <v>0.333</v>
+        <v>0.358</v>
       </c>
       <c r="T24" t="n">
-        <v>0.118</v>
+        <v>0.171</v>
       </c>
       <c r="U24" t="n">
-        <v>0.026</v>
+        <v>0.056</v>
       </c>
       <c r="V24" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AK24" t="n">
         <v>0.004</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0.002</v>
       </c>
       <c r="AL24" t="n">
         <v>0.002</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.379</v>
+        <v>0.491</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.332</v>
+        <v>0.429</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.316</v>
+        <v>0.451</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.339</v>
+        <v>0.475</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.347</v>
+        <v>0.46</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.374</v>
+        <v>0.504</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.438</v>
+        <v>0.458</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.538</v>
+        <v>0.431</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.29</v>
+        <v>0.186</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.102</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>823075</v>
+        <v>822828</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4290,150 +4290,150 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.383</v>
+        <v>3.94</v>
       </c>
       <c r="G25" t="n">
-        <v>0.467</v>
+        <v>0.46</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="I25" t="n">
-        <v>0.233</v>
+        <v>0.175</v>
       </c>
       <c r="J25" t="n">
-        <v>0.113</v>
+        <v>0.096</v>
       </c>
       <c r="K25" t="n">
-        <v>0.294</v>
+        <v>0.302</v>
       </c>
       <c r="L25" t="n">
-        <v>0.879</v>
+        <v>0.986</v>
       </c>
       <c r="M25" t="n">
-        <v>0.059</v>
+        <v>0.111</v>
       </c>
       <c r="N25" t="n">
-        <v>1.76</v>
+        <v>1.561</v>
       </c>
       <c r="O25" t="n">
-        <v>5.018</v>
+        <v>4.821</v>
       </c>
       <c r="P25" t="n">
-        <v>4.19</v>
+        <v>3.382</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.104</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>0.432</v>
+        <v>0.372</v>
       </c>
       <c r="S25" t="n">
-        <v>0.348</v>
+        <v>0.369</v>
       </c>
       <c r="T25" t="n">
-        <v>0.15</v>
+        <v>0.183</v>
       </c>
       <c r="U25" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="V25" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="W25" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="X25" t="n">
-        <v>0.06</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.094</v>
+        <v>0.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.138</v>
+        <v>0.148</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.144</v>
+        <v>0.152</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.114</v>
+        <v>0.112</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.09</v>
+        <v>0.093</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.073</v>
+        <v>0.057</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.025</v>
+        <v>0.018</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.591</v>
+        <v>0.458</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.487</v>
+        <v>0.396</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.516</v>
+        <v>0.389</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.52</v>
+        <v>0.431</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.516</v>
+        <v>0.385</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.493</v>
+        <v>0.464</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.407</v>
+        <v>0.435</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.424</v>
+        <v>0.495</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.211</v>
+        <v>0.264</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.102</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>823317</v>
+        <v>823154</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4447,150 +4447,150 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SD </t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.62</v>
+        <v>4.426</v>
       </c>
       <c r="G26" t="n">
-        <v>0.711</v>
+        <v>0.574</v>
       </c>
       <c r="H26" t="n">
-        <v>0.137</v>
+        <v>0.11</v>
       </c>
       <c r="I26" t="n">
-        <v>0.378</v>
+        <v>0.279</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="K26" t="n">
-        <v>0.113</v>
+        <v>0.21</v>
       </c>
       <c r="L26" t="n">
-        <v>1.081</v>
+        <v>1.112</v>
       </c>
       <c r="M26" t="n">
-        <v>0.108</v>
+        <v>0.079</v>
       </c>
       <c r="N26" t="n">
-        <v>1.37</v>
+        <v>1.356</v>
       </c>
       <c r="O26" t="n">
-        <v>5.913</v>
+        <v>4.782</v>
       </c>
       <c r="P26" t="n">
-        <v>3.161</v>
+        <v>4.649</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.854</v>
+        <v>8.77</v>
       </c>
       <c r="R26" t="n">
-        <v>0.353</v>
+        <v>0.324</v>
       </c>
       <c r="S26" t="n">
-        <v>0.356</v>
+        <v>0.372</v>
       </c>
       <c r="T26" t="n">
-        <v>0.183</v>
+        <v>0.21</v>
       </c>
       <c r="U26" t="n">
-        <v>0.079</v>
+        <v>0.065</v>
       </c>
       <c r="V26" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="W26" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AK26" t="n">
         <v>0.006</v>
       </c>
-      <c r="X26" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.008</v>
-      </c>
       <c r="AL26" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AM26" t="n">
         <v>0.004</v>
       </c>
-      <c r="AM26" t="n">
-        <v>0.007</v>
-      </c>
       <c r="AN26" t="n">
-        <v>0.547</v>
+        <v>0.515</v>
       </c>
       <c r="AO26" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AS26" t="n">
         <v>0.491</v>
       </c>
-      <c r="AP26" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.5629999999999999</v>
-      </c>
       <c r="AT26" t="n">
-        <v>0.594</v>
+        <v>0.508</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.579</v>
+        <v>0.513</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.184</v>
+        <v>0.238</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.111</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>823642</v>
+        <v>823479</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4604,150 +4604,150 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.59</v>
+        <v>4.543</v>
       </c>
       <c r="G27" t="n">
-        <v>0.574</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0.121</v>
+        <v>0.113</v>
       </c>
       <c r="I27" t="n">
-        <v>0.245</v>
+        <v>0.267</v>
       </c>
       <c r="J27" t="n">
-        <v>0.107</v>
+        <v>0.079</v>
       </c>
       <c r="K27" t="n">
-        <v>0.184</v>
+        <v>0.25</v>
       </c>
       <c r="L27" t="n">
-        <v>0.768</v>
+        <v>1.066</v>
       </c>
       <c r="M27" t="n">
-        <v>0.083</v>
+        <v>0.112</v>
       </c>
       <c r="N27" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
-        <v>4.82</v>
+        <v>5.319</v>
       </c>
       <c r="P27" t="n">
-        <v>3.662</v>
+        <v>3.988</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.741</v>
+        <v>7.232</v>
       </c>
       <c r="R27" t="n">
-        <v>0.458</v>
+        <v>0.344</v>
       </c>
       <c r="S27" t="n">
         <v>0.367</v>
       </c>
       <c r="T27" t="n">
-        <v>0.133</v>
+        <v>0.192</v>
       </c>
       <c r="U27" t="n">
-        <v>0.036</v>
+        <v>0.075</v>
       </c>
       <c r="V27" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="X27" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="Y27" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.134</v>
       </c>
-      <c r="Z27" t="n">
-        <v>0.155</v>
-      </c>
       <c r="AA27" t="n">
-        <v>0.17</v>
+        <v>0.147</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.113</v>
+        <v>0.114</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.076</v>
+        <v>0.103</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.053</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.027</v>
+        <v>0.051</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.02</v>
+        <v>0.031</v>
       </c>
       <c r="AH27" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI27" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.005</v>
-      </c>
       <c r="AK27" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.388</v>
+        <v>0.518</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.397</v>
+        <v>0.443</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.385</v>
+        <v>0.505</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.377</v>
+        <v>0.506</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.384</v>
+        <v>0.502</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.405</v>
+        <v>0.55</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.416</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.203</v>
+        <v>0.239</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>824126</v>
+        <v>823804</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4761,150 +4761,150 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC </t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CHW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.326</v>
+        <v>4.673</v>
       </c>
       <c r="G28" t="n">
-        <v>0.627</v>
+        <v>0.628</v>
       </c>
       <c r="H28" t="n">
-        <v>0.107</v>
+        <v>0.129</v>
       </c>
       <c r="I28" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>4.453</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7.324</v>
+      </c>
+      <c r="R28" t="n">
         <v>0.338</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.276</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.486</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4.979</v>
-      </c>
-      <c r="P28" t="n">
-        <v>5.047</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.266</v>
-      </c>
       <c r="S28" t="n">
-        <v>0.363</v>
+        <v>0.382</v>
       </c>
       <c r="T28" t="n">
-        <v>0.245</v>
+        <v>0.187</v>
       </c>
       <c r="U28" t="n">
-        <v>0.091</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="W28" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="X28" t="n">
-        <v>0.03</v>
+        <v>0.047</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.059</v>
+        <v>0.081</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.094</v>
+        <v>0.128</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.121</v>
+        <v>0.138</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.143</v>
+        <v>0.14</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.129</v>
+        <v>0.124</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.098</v>
+        <v>0.08</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.051</v>
+        <v>0.035</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.036</v>
+        <v>0.023</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.023</v>
+        <v>0.015</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AN28" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="AR28" t="n">
         <v>0.52</v>
       </c>
-      <c r="AO28" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0.61</v>
-      </c>
       <c r="AS28" t="n">
-        <v>0.594</v>
+        <v>0.528</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.645</v>
+        <v>0.554</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.648</v>
+        <v>0.621</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.249</v>
+        <v>0.239</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>824293</v>
+        <v>823966</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4918,150 +4918,150 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.586</v>
+        <v>3.422</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H29" t="n">
-        <v>0.125</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.239</v>
+        <v>0.136</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1</v>
+        <v>0.116</v>
       </c>
       <c r="K29" t="n">
-        <v>0.194</v>
+        <v>0.338</v>
       </c>
       <c r="L29" t="n">
-        <v>0.666</v>
+        <v>1.132</v>
       </c>
       <c r="M29" t="n">
-        <v>0.138</v>
+        <v>0.092</v>
       </c>
       <c r="N29" t="n">
-        <v>1.399</v>
+        <v>1.127</v>
       </c>
       <c r="O29" t="n">
-        <v>4.911</v>
+        <v>3.782</v>
       </c>
       <c r="P29" t="n">
-        <v>3.278</v>
+        <v>3.285</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.57</v>
+        <v>10.472</v>
       </c>
       <c r="R29" t="n">
-        <v>0.513</v>
+        <v>0.323</v>
       </c>
       <c r="S29" t="n">
-        <v>0.344</v>
+        <v>0.366</v>
       </c>
       <c r="T29" t="n">
-        <v>0.112</v>
+        <v>0.205</v>
       </c>
       <c r="U29" t="n">
-        <v>0.026</v>
+        <v>0.076</v>
       </c>
       <c r="V29" t="n">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="W29" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>0.001</v>
       </c>
-      <c r="X29" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.005</v>
-      </c>
       <c r="AK29" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AL29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AM29" t="n">
         <v>0.002</v>
       </c>
-      <c r="AM29" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AN29" t="n">
-        <v>0.382</v>
+        <v>0.388</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.367</v>
+        <v>0.302</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.377</v>
+        <v>0.337</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.353</v>
+        <v>0.316</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.378</v>
+        <v>0.337</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.413</v>
+        <v>0.375</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.403</v>
+        <v>0.433</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.466</v>
+        <v>0.459</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.217</v>
+        <v>0.3</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.134</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>824696</v>
+        <v>824533</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5075,150 +5075,150 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.776</v>
+        <v>4.212</v>
       </c>
       <c r="G30" t="n">
-        <v>0.516</v>
+        <v>0.544</v>
       </c>
       <c r="H30" t="n">
-        <v>0.093</v>
+        <v>0.099</v>
       </c>
       <c r="I30" t="n">
-        <v>0.277</v>
+        <v>0.242</v>
       </c>
       <c r="J30" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="K30" t="n">
-        <v>0.277</v>
+        <v>0.22</v>
       </c>
       <c r="L30" t="n">
-        <v>1.453</v>
+        <v>0.86</v>
       </c>
       <c r="M30" t="n">
-        <v>0.129</v>
+        <v>0.126</v>
       </c>
       <c r="N30" t="n">
-        <v>1.695</v>
+        <v>1.302</v>
       </c>
       <c r="O30" t="n">
-        <v>5.325</v>
+        <v>4.875</v>
       </c>
       <c r="P30" t="n">
-        <v>5.369</v>
+        <v>4.863</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.782</v>
+        <v>9.882999999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>0.229</v>
+        <v>0.423</v>
       </c>
       <c r="S30" t="n">
-        <v>0.346</v>
+        <v>0.367</v>
       </c>
       <c r="T30" t="n">
-        <v>0.244</v>
+        <v>0.151</v>
       </c>
       <c r="U30" t="n">
-        <v>0.124</v>
+        <v>0.049</v>
       </c>
       <c r="V30" t="n">
-        <v>0.04</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>0.017</v>
+        <v>0.002</v>
       </c>
       <c r="X30" t="n">
-        <v>0.026</v>
+        <v>0.064</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.062</v>
+        <v>0.104</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.144</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.101</v>
+        <v>0.148</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.12</v>
+        <v>0.141</v>
       </c>
       <c r="AC30" t="n">
         <v>0.118</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.117</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.096</v>
+        <v>0.063</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.076</v>
+        <v>0.051</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.063</v>
+        <v>0.034</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.043</v>
+        <v>0.019</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.592</v>
+        <v>0.462</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.587</v>
+        <v>0.441</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.608</v>
+        <v>0.399</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.599</v>
+        <v>0.443</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.64</v>
+        <v>0.451</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.704</v>
+        <v>0.486</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.742</v>
+        <v>0.487</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.375</v>
+        <v>0.268</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.112</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>824938</v>
+        <v>824859</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -5232,145 +5232,145 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t xml:space="preserve">SF </t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.101</v>
+        <v>4.267</v>
       </c>
       <c r="G31" t="n">
-        <v>0.57</v>
+        <v>0.517</v>
       </c>
       <c r="H31" t="n">
-        <v>0.113</v>
+        <v>0.1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.273</v>
+        <v>0.249</v>
       </c>
       <c r="J31" t="n">
-        <v>0.095</v>
+        <v>0.102</v>
       </c>
       <c r="K31" t="n">
-        <v>0.21</v>
+        <v>0.261</v>
       </c>
       <c r="L31" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="M31" t="n">
-        <v>0.127</v>
+        <v>0.09</v>
       </c>
       <c r="N31" t="n">
-        <v>1.688</v>
+        <v>1.612</v>
       </c>
       <c r="O31" t="n">
-        <v>4.819</v>
+        <v>5.32</v>
       </c>
       <c r="P31" t="n">
-        <v>3.449</v>
+        <v>4.395</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.812</v>
+        <v>7.787</v>
       </c>
       <c r="R31" t="n">
-        <v>0.405</v>
+        <v>0.52</v>
       </c>
       <c r="S31" t="n">
-        <v>0.358</v>
+        <v>0.324</v>
       </c>
       <c r="T31" t="n">
-        <v>0.171</v>
+        <v>0.121</v>
       </c>
       <c r="U31" t="n">
-        <v>0.056</v>
+        <v>0.027</v>
       </c>
       <c r="V31" t="n">
         <v>0.008</v>
       </c>
       <c r="W31" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="X31" t="n">
-        <v>0.063</v>
+        <v>0.058</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.141</v>
+        <v>0.132</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.119</v>
+        <v>0.111</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.099</v>
+        <v>0.083</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.038</v>
+        <v>0.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AK31" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AL31" t="n">
         <v>0.004</v>
       </c>
-      <c r="AL31" t="n">
-        <v>0.002</v>
-      </c>
       <c r="AM31" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.491</v>
+        <v>0.503</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.429</v>
+        <v>0.44</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.451</v>
+        <v>0.446</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.475</v>
+        <v>0.459</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.504</v>
+        <v>0.481</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.458</v>
+        <v>0.481</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.431</v>
+        <v>0.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.186</v>
+        <v>0.248</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.113</v>
+        <v>0.126</v>
       </c>
     </row>
   </sheetData>
